--- a/october_2025/2d_sig_clustering_subject_lvl_all_data_oct25.xlsx
+++ b/october_2025/2d_sig_clustering_subject_lvl_all_data_oct25.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="634" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1448" uniqueCount="412">
   <si>
     <t>clusterLabels</t>
   </si>
@@ -748,6 +748,507 @@
   </si>
   <si>
     <t>98734_story_3.mat</t>
+  </si>
+  <si>
+    <t>88407_story_17.mat</t>
+  </si>
+  <si>
+    <t>16222_story_5.mat</t>
+  </si>
+  <si>
+    <t>94591_story_12.mat</t>
+  </si>
+  <si>
+    <t>36548_story_17.mat</t>
+  </si>
+  <si>
+    <t>37034_story_2.mat</t>
+  </si>
+  <si>
+    <t>37213_story_10.mat</t>
+  </si>
+  <si>
+    <t>49261_story_10.mat</t>
+  </si>
+  <si>
+    <t>38557_story_21.mat</t>
+  </si>
+  <si>
+    <t>65976_story_22.mat</t>
+  </si>
+  <si>
+    <t>28004_story_4.mat</t>
+  </si>
+  <si>
+    <t>49261_story_3.mat</t>
+  </si>
+  <si>
+    <t>66201_story_1.mat</t>
+  </si>
+  <si>
+    <t>76926_story_1.mat</t>
+  </si>
+  <si>
+    <t>15855_story_1.mat</t>
+  </si>
+  <si>
+    <t>46141_story_1.mat</t>
+  </si>
+  <si>
+    <t>71391_story_1.mat</t>
+  </si>
+  <si>
+    <t>29335_story_10.mat</t>
+  </si>
+  <si>
+    <t>76926_story_22.mat</t>
+  </si>
+  <si>
+    <t>28004_story_1.mat</t>
+  </si>
+  <si>
+    <t>46141_story_5.mat</t>
+  </si>
+  <si>
+    <t>66259_story_2.mat</t>
+  </si>
+  <si>
+    <t>45531_story_1.mat</t>
+  </si>
+  <si>
+    <t>95786_story_6.mat</t>
+  </si>
+  <si>
+    <t>65976_story_1.mat</t>
+  </si>
+  <si>
+    <t>46141_story_12.mat</t>
+  </si>
+  <si>
+    <t>71966_story_16.mat</t>
+  </si>
+  <si>
+    <t>21003_story_1.mat</t>
+  </si>
+  <si>
+    <t>28004_story_16.mat</t>
+  </si>
+  <si>
+    <t>66259_story_5.mat</t>
+  </si>
+  <si>
+    <t>58215_story_20.mat</t>
+  </si>
+  <si>
+    <t>11464_story_20.mat</t>
+  </si>
+  <si>
+    <t>mergedaa</t>
+  </si>
+  <si>
+    <t>negative</t>
+  </si>
+  <si>
+    <t>positive</t>
+  </si>
+  <si>
+    <t>82826_story_18.mat</t>
+  </si>
+  <si>
+    <t>44694_story_18.mat</t>
+  </si>
+  <si>
+    <t>86788_story_9.mat</t>
+  </si>
+  <si>
+    <t>65976_story_18.mat</t>
+  </si>
+  <si>
+    <t>38849_story_12.mat</t>
+  </si>
+  <si>
+    <t>48359_story_3.mat</t>
+  </si>
+  <si>
+    <t>69566_story_23.mat</t>
+  </si>
+  <si>
+    <t>71391_story_2.mat</t>
+  </si>
+  <si>
+    <t>35993_story_18.mat</t>
+  </si>
+  <si>
+    <t>42347_story_10.mat</t>
+  </si>
+  <si>
+    <t>48359_story_2.mat</t>
+  </si>
+  <si>
+    <t>49040_story_16.mat</t>
+  </si>
+  <si>
+    <t>69566_story_16.mat</t>
+  </si>
+  <si>
+    <t>79935_story_14.mat</t>
+  </si>
+  <si>
+    <t>86528_story_18.mat</t>
+  </si>
+  <si>
+    <t>64094_story_15.mat</t>
+  </si>
+  <si>
+    <t>79985_story_19.mat</t>
+  </si>
+  <si>
+    <t>87126_story_24.mat</t>
+  </si>
+  <si>
+    <t>24785_story_4.mat</t>
+  </si>
+  <si>
+    <t>69727_story_8.mat</t>
+  </si>
+  <si>
+    <t>69727_story_3.mat</t>
+  </si>
+  <si>
+    <t>38557_story_1.mat</t>
+  </si>
+  <si>
+    <t>68254_story_3.mat</t>
+  </si>
+  <si>
+    <t>71966_story_1.mat</t>
+  </si>
+  <si>
+    <t>51530_story_1.mat</t>
+  </si>
+  <si>
+    <t>45737_story_1.mat</t>
+  </si>
+  <si>
+    <t>69727_story_1.mat</t>
+  </si>
+  <si>
+    <t>78005_story_3.mat</t>
+  </si>
+  <si>
+    <t>68254_story_5.mat</t>
+  </si>
+  <si>
+    <t>36548_story_28.mat</t>
+  </si>
+  <si>
+    <t>98375_story_10.mat</t>
+  </si>
+  <si>
+    <t>78005_story_2.mat</t>
+  </si>
+  <si>
+    <t>48359_story_18.mat</t>
+  </si>
+  <si>
+    <t>15855_story_17.mat</t>
+  </si>
+  <si>
+    <t>21003_story_12.mat</t>
+  </si>
+  <si>
+    <t>71391_story_10.mat</t>
+  </si>
+  <si>
+    <t>79935_story_9.mat</t>
+  </si>
+  <si>
+    <t>86528_story_3.mat</t>
+  </si>
+  <si>
+    <t>30401_story_16.mat</t>
+  </si>
+  <si>
+    <t>66201_story_10.mat</t>
+  </si>
+  <si>
+    <t>41117_story_22.mat</t>
+  </si>
+  <si>
+    <t>86788_story_5.mat</t>
+  </si>
+  <si>
+    <t>39508_story_7.mat</t>
+  </si>
+  <si>
+    <t>66939_story_7.mat</t>
+  </si>
+  <si>
+    <t>79605_story_10.mat</t>
+  </si>
+  <si>
+    <t>61074_story_12.mat</t>
+  </si>
+  <si>
+    <t>66259_story_10.mat</t>
+  </si>
+  <si>
+    <t>87126_story_9.mat</t>
+  </si>
+  <si>
+    <t>37520_story_15.mat</t>
+  </si>
+  <si>
+    <t>55094_story_12.mat</t>
+  </si>
+  <si>
+    <t>98375_story_14.mat</t>
+  </si>
+  <si>
+    <t>69727_story_17.mat</t>
+  </si>
+  <si>
+    <t>81930_story_17.mat</t>
+  </si>
+  <si>
+    <t>40879_story_5.mat</t>
+  </si>
+  <si>
+    <t>98865_story_1.mat</t>
+  </si>
+  <si>
+    <t>29335_story_13.mat</t>
+  </si>
+  <si>
+    <t>49797_story_10.mat</t>
+  </si>
+  <si>
+    <t>65944_story_19.mat</t>
+  </si>
+  <si>
+    <t>82440_story_14.mat</t>
+  </si>
+  <si>
+    <t>30401_story_1.mat</t>
+  </si>
+  <si>
+    <t>48359_story_1.mat</t>
+  </si>
+  <si>
+    <t>58215_story_1.mat</t>
+  </si>
+  <si>
+    <t>78005_story_5.mat</t>
+  </si>
+  <si>
+    <t>15093_story_5.mat</t>
+  </si>
+  <si>
+    <t>19392_story_1.mat</t>
+  </si>
+  <si>
+    <t>21188_story_15.mat</t>
+  </si>
+  <si>
+    <t>31657_story_20.mat</t>
+  </si>
+  <si>
+    <t>98865_story_29.mat</t>
+  </si>
+  <si>
+    <t>31657_story_12.mat</t>
+  </si>
+  <si>
+    <t>35993_story_10.mat</t>
+  </si>
+  <si>
+    <t>49040_story_21.mat</t>
+  </si>
+  <si>
+    <t>81930_story_16.mat</t>
+  </si>
+  <si>
+    <t>49797_story_1.mat</t>
+  </si>
+  <si>
+    <t>66939_story_5.mat</t>
+  </si>
+  <si>
+    <t>44694_story_2.mat</t>
+  </si>
+  <si>
+    <t>38889_story_1.mat</t>
+  </si>
+  <si>
+    <t>83158_story_18.mat</t>
+  </si>
+  <si>
+    <t>35993_story_16.mat</t>
+  </si>
+  <si>
+    <t>94483_story_24.mat</t>
+  </si>
+  <si>
+    <t>38557_story_8.mat</t>
+  </si>
+  <si>
+    <t>31657_story_23.mat</t>
+  </si>
+  <si>
+    <t>28690_story_5.mat</t>
+  </si>
+  <si>
+    <t>28004_story_19.mat</t>
+  </si>
+  <si>
+    <t>cost_cost</t>
+  </si>
+  <si>
+    <t>58215_story_2.mat</t>
+  </si>
+  <si>
+    <t>90653_story_6.mat</t>
+  </si>
+  <si>
+    <t>93964_story_21.mat</t>
+  </si>
+  <si>
+    <t>95786_story_21.mat</t>
+  </si>
+  <si>
+    <t>58215_story_5.mat</t>
+  </si>
+  <si>
+    <t>70388_story_3.mat</t>
+  </si>
+  <si>
+    <t>42347_story_7.mat</t>
+  </si>
+  <si>
+    <t>21188_story_19.mat</t>
+  </si>
+  <si>
+    <t>18108_story_20.mat</t>
+  </si>
+  <si>
+    <t>19392_story_2.mat</t>
+  </si>
+  <si>
+    <t>30401_story_12.mat</t>
+  </si>
+  <si>
+    <t>50679_story_17.mat</t>
+  </si>
+  <si>
+    <t>51530_story_11.mat</t>
+  </si>
+  <si>
+    <t>21188_story_9.mat</t>
+  </si>
+  <si>
+    <t>37520_story_19.mat</t>
+  </si>
+  <si>
+    <t>37612_story_16.mat</t>
+  </si>
+  <si>
+    <t>15855_story_5.mat</t>
+  </si>
+  <si>
+    <t>51530_story_5.mat</t>
+  </si>
+  <si>
+    <t>49040_story_1.mat</t>
+  </si>
+  <si>
+    <t>41117_story_1.mat</t>
+  </si>
+  <si>
+    <t>40879_story_25.mat</t>
+  </si>
+  <si>
+    <t>38557_story_18.mat</t>
+  </si>
+  <si>
+    <t>94483_story_10.mat</t>
+  </si>
+  <si>
+    <t>15093_story_10.mat</t>
+  </si>
+  <si>
+    <t>38889_story_10.mat</t>
+  </si>
+  <si>
+    <t>90653_story_18.mat</t>
+  </si>
+  <si>
+    <t>55094_story_22.mat</t>
+  </si>
+  <si>
+    <t>83158_story_22.mat</t>
+  </si>
+  <si>
+    <t>45737_story_5.mat</t>
+  </si>
+  <si>
+    <t>49040_story_12.mat</t>
+  </si>
+  <si>
+    <t>64094_story_2.mat</t>
+  </si>
+  <si>
+    <t>94483_story_22.mat</t>
+  </si>
+  <si>
+    <t>98375_story_9.mat</t>
+  </si>
+  <si>
+    <t>87126_story_17.mat</t>
+  </si>
+  <si>
+    <t>16222_story_6.mat</t>
+  </si>
+  <si>
+    <t>15093_story_1.mat</t>
+  </si>
+  <si>
+    <t>82826_story_22.mat</t>
+  </si>
+  <si>
+    <t>49261_story_16.mat</t>
+  </si>
+  <si>
+    <t>55094_story_17.mat</t>
+  </si>
+  <si>
+    <t>68254_story_7.mat</t>
+  </si>
+  <si>
+    <t>71966_story_21.mat</t>
+  </si>
+  <si>
+    <t>51530_story_24.mat</t>
+  </si>
+  <si>
+    <t>51530_story_13.mat</t>
+  </si>
+  <si>
+    <t>78005_story_8.mat</t>
+  </si>
+  <si>
+    <t>87126_story_18.mat</t>
+  </si>
+  <si>
+    <t>21188_story_20.mat</t>
+  </si>
+  <si>
+    <t>82826_story_17.mat</t>
+  </si>
+  <si>
+    <t>19189_story_12.mat</t>
+  </si>
+  <si>
+    <t>58215_story_23.mat</t>
   </si>
 </sst>
 </file>
@@ -793,15 +1294,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F315"/>
+  <dimension ref="A1:F722"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.88671875" customWidth="true"/>
     <col min="2" max="2" width="13.21875" customWidth="true"/>
-    <col min="3" max="3" width="13.5546875" customWidth="true"/>
-    <col min="4" max="4" width="13.5546875" customWidth="true"/>
+    <col min="3" max="3" width="15.21875" customWidth="true"/>
+    <col min="4" max="4" width="14.21875" customWidth="true"/>
     <col min="5" max="5" width="2" customWidth="true"/>
-    <col min="6" max="6" width="17.6640625" customWidth="true"/>
+    <col min="6" max="6" width="17.33203125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7104,6 +7605,8146 @@
         <v>36</v>
       </c>
     </row>
+    <row r="316">
+      <c r="A316" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="B316" s="0">
+        <v>73.815056741382193</v>
+      </c>
+      <c r="C316" s="0">
+        <v>17.38416888225915</v>
+      </c>
+      <c r="D316" s="0">
+        <v>-9.0429346622393769</v>
+      </c>
+      <c r="E316" s="0">
+        <v>1</v>
+      </c>
+      <c r="F316" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="B317" s="0">
+        <v>90.915149192809736</v>
+      </c>
+      <c r="C317" s="0">
+        <v>20.331371289916447</v>
+      </c>
+      <c r="D317" s="0">
+        <v>5.0978545661561716</v>
+      </c>
+      <c r="E317" s="0">
+        <v>1</v>
+      </c>
+      <c r="F317" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="0" t="s">
+        <v>247</v>
+      </c>
+      <c r="B318" s="0">
+        <v>74.817463200550989</v>
+      </c>
+      <c r="C318" s="0">
+        <v>17.099492747644689</v>
+      </c>
+      <c r="D318" s="0">
+        <v>-1.8338200685258319</v>
+      </c>
+      <c r="E318" s="0">
+        <v>1</v>
+      </c>
+      <c r="F318" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="B319" s="0">
+        <v>60.260798960516688</v>
+      </c>
+      <c r="C319" s="0">
+        <v>12.041922321899479</v>
+      </c>
+      <c r="D319" s="0">
+        <v>0.046821385063151824</v>
+      </c>
+      <c r="E319" s="0">
+        <v>1</v>
+      </c>
+      <c r="F319" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="B320" s="0">
+        <v>84.924741269498</v>
+      </c>
+      <c r="C320" s="0">
+        <v>44.224787246208962</v>
+      </c>
+      <c r="D320" s="0">
+        <v>-0.080804127871343556</v>
+      </c>
+      <c r="E320" s="0">
+        <v>1</v>
+      </c>
+      <c r="F320" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="0" t="s">
+        <v>248</v>
+      </c>
+      <c r="B321" s="0">
+        <v>79.392145089607254</v>
+      </c>
+      <c r="C321" s="0">
+        <v>19.020235128597815</v>
+      </c>
+      <c r="D321" s="0">
+        <v>-3.1205031260198299</v>
+      </c>
+      <c r="E321" s="0">
+        <v>1</v>
+      </c>
+      <c r="F321" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="B322" s="0">
+        <v>77.535608858948265</v>
+      </c>
+      <c r="C322" s="0">
+        <v>19.739909685858837</v>
+      </c>
+      <c r="D322" s="0">
+        <v>0.53635785241183109</v>
+      </c>
+      <c r="E322" s="0">
+        <v>1</v>
+      </c>
+      <c r="F322" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="B323" s="0">
+        <v>60.260798960516688</v>
+      </c>
+      <c r="C323" s="0">
+        <v>12.041922321899479</v>
+      </c>
+      <c r="D323" s="0">
+        <v>0.046821385063151824</v>
+      </c>
+      <c r="E323" s="0">
+        <v>1</v>
+      </c>
+      <c r="F323" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="B324" s="0">
+        <v>84.924741269498</v>
+      </c>
+      <c r="C324" s="0">
+        <v>44.224787246208962</v>
+      </c>
+      <c r="D324" s="0">
+        <v>-0.080804127871343556</v>
+      </c>
+      <c r="E324" s="0">
+        <v>1</v>
+      </c>
+      <c r="F324" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="B325" s="0">
+        <v>77.733575940375061</v>
+      </c>
+      <c r="C325" s="0">
+        <v>18.396445151128066</v>
+      </c>
+      <c r="D325" s="0">
+        <v>-2.8086208898542306</v>
+      </c>
+      <c r="E325" s="0">
+        <v>1</v>
+      </c>
+      <c r="F325" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="0" t="s">
+        <v>167</v>
+      </c>
+      <c r="B326" s="0">
+        <v>89.921557415458182</v>
+      </c>
+      <c r="C326" s="0">
+        <v>45.183222135244272</v>
+      </c>
+      <c r="D326" s="0">
+        <v>-4.1174038243444597</v>
+      </c>
+      <c r="E326" s="0">
+        <v>1</v>
+      </c>
+      <c r="F326" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="B327" s="0">
+        <v>63.733125258984593</v>
+      </c>
+      <c r="C327" s="0">
+        <v>24.970765875572219</v>
+      </c>
+      <c r="D327" s="0">
+        <v>-4.7761094552404328</v>
+      </c>
+      <c r="E327" s="0">
+        <v>1</v>
+      </c>
+      <c r="F327" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="B328" s="0">
+        <v>79.174426628879971</v>
+      </c>
+      <c r="C328" s="0">
+        <v>19.299119507016758</v>
+      </c>
+      <c r="D328" s="0">
+        <v>-6.7343872587022258</v>
+      </c>
+      <c r="E328" s="0">
+        <v>1</v>
+      </c>
+      <c r="F328" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="0" t="s">
+        <v>250</v>
+      </c>
+      <c r="B329" s="0">
+        <v>74.714441569299595</v>
+      </c>
+      <c r="C329" s="0">
+        <v>18.732565883166643</v>
+      </c>
+      <c r="D329" s="0">
+        <v>-2.1689539655017835</v>
+      </c>
+      <c r="E329" s="0">
+        <v>1</v>
+      </c>
+      <c r="F329" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="0" t="s">
+        <v>251</v>
+      </c>
+      <c r="B330" s="0">
+        <v>87.117697717025834</v>
+      </c>
+      <c r="C330" s="0">
+        <v>21.371717257425445</v>
+      </c>
+      <c r="D330" s="0">
+        <v>-2.2707524273785662</v>
+      </c>
+      <c r="E330" s="0">
+        <v>1</v>
+      </c>
+      <c r="F330" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="B331" s="0">
+        <v>84.924741269498</v>
+      </c>
+      <c r="C331" s="0">
+        <v>44.224787246208962</v>
+      </c>
+      <c r="D331" s="0">
+        <v>-0.080804127871343556</v>
+      </c>
+      <c r="E331" s="0">
+        <v>1</v>
+      </c>
+      <c r="F331" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="0" t="s">
+        <v>252</v>
+      </c>
+      <c r="B332" s="0">
+        <v>77.693828102428824</v>
+      </c>
+      <c r="C332" s="0">
+        <v>16.774935974791696</v>
+      </c>
+      <c r="D332" s="0">
+        <v>-2.9177799312642061</v>
+      </c>
+      <c r="E332" s="0">
+        <v>1</v>
+      </c>
+      <c r="F332" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="0" t="s">
+        <v>253</v>
+      </c>
+      <c r="B333" s="0">
+        <v>80.426085883285367</v>
+      </c>
+      <c r="C333" s="0">
+        <v>42.031820588015535</v>
+      </c>
+      <c r="D333" s="0">
+        <v>4.5743623272025005</v>
+      </c>
+      <c r="E333" s="0">
+        <v>1</v>
+      </c>
+      <c r="F333" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="B334" s="0">
+        <v>77.535608858948265</v>
+      </c>
+      <c r="C334" s="0">
+        <v>19.739909685858837</v>
+      </c>
+      <c r="D334" s="0">
+        <v>0.53635785241183109</v>
+      </c>
+      <c r="E334" s="0">
+        <v>1</v>
+      </c>
+      <c r="F334" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="0" t="s">
+        <v>254</v>
+      </c>
+      <c r="B335" s="0">
+        <v>78.502761097718064</v>
+      </c>
+      <c r="C335" s="0">
+        <v>58.124499983527699</v>
+      </c>
+      <c r="D335" s="0">
+        <v>-15.555344364680222</v>
+      </c>
+      <c r="E335" s="0">
+        <v>1</v>
+      </c>
+      <c r="F335" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="0" t="s">
+        <v>255</v>
+      </c>
+      <c r="B336" s="0">
+        <v>86.928352928765307</v>
+      </c>
+      <c r="C336" s="0">
+        <v>19.261621760386156</v>
+      </c>
+      <c r="D336" s="0">
+        <v>0.028815059329602467</v>
+      </c>
+      <c r="E336" s="0">
+        <v>1</v>
+      </c>
+      <c r="F336" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="0" t="s">
+        <v>256</v>
+      </c>
+      <c r="B337" s="0">
+        <v>79.532313359149143</v>
+      </c>
+      <c r="C337" s="0">
+        <v>19.426619460232477</v>
+      </c>
+      <c r="D337" s="0">
+        <v>-1.1417546040348214</v>
+      </c>
+      <c r="E337" s="0">
+        <v>1</v>
+      </c>
+      <c r="F337" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="0" t="s">
+        <v>257</v>
+      </c>
+      <c r="B338" s="0">
+        <v>79.315791844387874</v>
+      </c>
+      <c r="C338" s="0">
+        <v>12.421298201472425</v>
+      </c>
+      <c r="D338" s="0">
+        <v>-1.3253343815195076</v>
+      </c>
+      <c r="E338" s="0">
+        <v>1</v>
+      </c>
+      <c r="F338" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="0" t="s">
+        <v>258</v>
+      </c>
+      <c r="B339" s="0">
+        <v>99.743064802902211</v>
+      </c>
+      <c r="C339" s="0">
+        <v>24.033675455113109</v>
+      </c>
+      <c r="D339" s="0">
+        <v>-0.43545471604776631</v>
+      </c>
+      <c r="E339" s="0">
+        <v>1</v>
+      </c>
+      <c r="F339" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="B340" s="0">
+        <v>92.360023556934692</v>
+      </c>
+      <c r="C340" s="0">
+        <v>21.638418333042669</v>
+      </c>
+      <c r="D340" s="0">
+        <v>-0.66473471015238006</v>
+      </c>
+      <c r="E340" s="0">
+        <v>1</v>
+      </c>
+      <c r="F340" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="B341" s="0">
+        <v>97.12919923352618</v>
+      </c>
+      <c r="C341" s="0">
+        <v>23.292071812694285</v>
+      </c>
+      <c r="D341" s="0">
+        <v>-0.51444243787836774</v>
+      </c>
+      <c r="E341" s="0">
+        <v>1</v>
+      </c>
+      <c r="F341" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="0" t="s">
+        <v>254</v>
+      </c>
+      <c r="B342" s="0">
+        <v>78.502761097718064</v>
+      </c>
+      <c r="C342" s="0">
+        <v>58.124499983527699</v>
+      </c>
+      <c r="D342" s="0">
+        <v>-15.555344364680222</v>
+      </c>
+      <c r="E342" s="0">
+        <v>1</v>
+      </c>
+      <c r="F342" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="0" t="s">
+        <v>256</v>
+      </c>
+      <c r="B343" s="0">
+        <v>79.41745280287914</v>
+      </c>
+      <c r="C343" s="0">
+        <v>19.698745858840624</v>
+      </c>
+      <c r="D343" s="0">
+        <v>-1.4114027853909841</v>
+      </c>
+      <c r="E343" s="0">
+        <v>1</v>
+      </c>
+      <c r="F343" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="0" t="s">
+        <v>257</v>
+      </c>
+      <c r="B344" s="0">
+        <v>79.315791844387874</v>
+      </c>
+      <c r="C344" s="0">
+        <v>12.421298201472425</v>
+      </c>
+      <c r="D344" s="0">
+        <v>-1.3253343815195076</v>
+      </c>
+      <c r="E344" s="0">
+        <v>1</v>
+      </c>
+      <c r="F344" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="0" t="s">
+        <v>180</v>
+      </c>
+      <c r="B345" s="0">
+        <v>96.781978550760371</v>
+      </c>
+      <c r="C345" s="0">
+        <v>23.128659975968013</v>
+      </c>
+      <c r="D345" s="0">
+        <v>-0.53274269686127285</v>
+      </c>
+      <c r="E345" s="0">
+        <v>1</v>
+      </c>
+      <c r="F345" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="0" t="s">
+        <v>179</v>
+      </c>
+      <c r="B346" s="0">
+        <v>98.065146384774238</v>
+      </c>
+      <c r="C346" s="0">
+        <v>49.538269909442214</v>
+      </c>
+      <c r="D346" s="0">
+        <v>-0.91127195975174369</v>
+      </c>
+      <c r="E346" s="0">
+        <v>1</v>
+      </c>
+      <c r="F346" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="B347" s="0">
+        <v>61.670487084068945</v>
+      </c>
+      <c r="C347" s="0">
+        <v>13.319049229245541</v>
+      </c>
+      <c r="D347" s="0">
+        <v>0.46030091321174399</v>
+      </c>
+      <c r="E347" s="0">
+        <v>1</v>
+      </c>
+      <c r="F347" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B348" s="0">
+        <v>96.725423554342527</v>
+      </c>
+      <c r="C348" s="0">
+        <v>22.645195956198361</v>
+      </c>
+      <c r="D348" s="0">
+        <v>-0.27545720137972757</v>
+      </c>
+      <c r="E348" s="0">
+        <v>1</v>
+      </c>
+      <c r="F348" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="0" t="s">
+        <v>262</v>
+      </c>
+      <c r="B349" s="0">
+        <v>103.88154181431466</v>
+      </c>
+      <c r="C349" s="0">
+        <v>25.907536365707045</v>
+      </c>
+      <c r="D349" s="0">
+        <v>-23.250367641141217</v>
+      </c>
+      <c r="E349" s="0">
+        <v>1</v>
+      </c>
+      <c r="F349" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="0" t="s">
+        <v>263</v>
+      </c>
+      <c r="B350" s="0">
+        <v>98.855823184087413</v>
+      </c>
+      <c r="C350" s="0">
+        <v>24.493303138206823</v>
+      </c>
+      <c r="D350" s="0">
+        <v>-4.0352106686753544</v>
+      </c>
+      <c r="E350" s="0">
+        <v>1</v>
+      </c>
+      <c r="F350" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="B351" s="0">
+        <v>81.721118380645137</v>
+      </c>
+      <c r="C351" s="0">
+        <v>12.83251184813885</v>
+      </c>
+      <c r="D351" s="0">
+        <v>-2.8164601147334052</v>
+      </c>
+      <c r="E351" s="0">
+        <v>1</v>
+      </c>
+      <c r="F351" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="B352" s="0">
+        <v>77.566666916305209</v>
+      </c>
+      <c r="C352" s="0">
+        <v>16.129411435557373</v>
+      </c>
+      <c r="D352" s="0">
+        <v>-1.0530434396061712</v>
+      </c>
+      <c r="E352" s="0">
+        <v>1</v>
+      </c>
+      <c r="F352" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="B353" s="0">
+        <v>79.01999543710842</v>
+      </c>
+      <c r="C353" s="0">
+        <v>19.710159965136942</v>
+      </c>
+      <c r="D353" s="0">
+        <v>-10.964806345917774</v>
+      </c>
+      <c r="E353" s="0">
+        <v>1</v>
+      </c>
+      <c r="F353" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="B354" s="0">
+        <v>99.508920012372016</v>
+      </c>
+      <c r="C354" s="0">
+        <v>49.836482162040426</v>
+      </c>
+      <c r="D354" s="0">
+        <v>0.17741783981695664</v>
+      </c>
+      <c r="E354" s="0">
+        <v>1</v>
+      </c>
+      <c r="F354" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="B355" s="0">
+        <v>77.16221902483727</v>
+      </c>
+      <c r="C355" s="0">
+        <v>17.938646224102335</v>
+      </c>
+      <c r="D355" s="0">
+        <v>-0.074266850092889025</v>
+      </c>
+      <c r="E355" s="0">
+        <v>1</v>
+      </c>
+      <c r="F355" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="0" t="s">
+        <v>155</v>
+      </c>
+      <c r="B356" s="0">
+        <v>81.13426254154885</v>
+      </c>
+      <c r="C356" s="0">
+        <v>12.006805631497144</v>
+      </c>
+      <c r="D356" s="0">
+        <v>0.12330341207312363</v>
+      </c>
+      <c r="E356" s="0">
+        <v>1</v>
+      </c>
+      <c r="F356" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="B357" s="0">
+        <v>94.736545889037529</v>
+      </c>
+      <c r="C357" s="0">
+        <v>52.245741735700541</v>
+      </c>
+      <c r="D357" s="0">
+        <v>2.5456250703478576</v>
+      </c>
+      <c r="E357" s="0">
+        <v>1</v>
+      </c>
+      <c r="F357" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="B358" s="0">
+        <v>96.916535030663638</v>
+      </c>
+      <c r="C358" s="0">
+        <v>21.404794641046784</v>
+      </c>
+      <c r="D358" s="0">
+        <v>-4.7143641044135407</v>
+      </c>
+      <c r="E358" s="0">
+        <v>1</v>
+      </c>
+      <c r="F358" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="B359" s="0">
+        <v>79.341520817089616</v>
+      </c>
+      <c r="C359" s="0">
+        <v>17.377557555737461</v>
+      </c>
+      <c r="D359" s="0">
+        <v>-2.8597752306082338</v>
+      </c>
+      <c r="E359" s="0">
+        <v>1</v>
+      </c>
+      <c r="F359" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="B360" s="0">
+        <v>97.245699533280089</v>
+      </c>
+      <c r="C360" s="0">
+        <v>50.171290981339297</v>
+      </c>
+      <c r="D360" s="0">
+        <v>-2.2422737616549129</v>
+      </c>
+      <c r="E360" s="0">
+        <v>1</v>
+      </c>
+      <c r="F360" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="0" t="s">
+        <v>167</v>
+      </c>
+      <c r="B361" s="0">
+        <v>99.676922792182907</v>
+      </c>
+      <c r="C361" s="0">
+        <v>50.630814479851765</v>
+      </c>
+      <c r="D361" s="0">
+        <v>-4.4158339024297364</v>
+      </c>
+      <c r="E361" s="0">
+        <v>1</v>
+      </c>
+      <c r="F361" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="B362" s="0">
+        <v>79.71193339917798</v>
+      </c>
+      <c r="C362" s="0">
+        <v>17.671778289471504</v>
+      </c>
+      <c r="D362" s="0">
+        <v>-1.8276674113123867</v>
+      </c>
+      <c r="E362" s="0">
+        <v>1</v>
+      </c>
+      <c r="F362" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="B363" s="0">
+        <v>78.782122198231093</v>
+      </c>
+      <c r="C363" s="0">
+        <v>16.1313841259249</v>
+      </c>
+      <c r="D363" s="0">
+        <v>-8.5341031359156112</v>
+      </c>
+      <c r="E363" s="0">
+        <v>1</v>
+      </c>
+      <c r="F363" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="B364" s="0">
+        <v>79.087878792056571</v>
+      </c>
+      <c r="C364" s="0">
+        <v>19.768288398832677</v>
+      </c>
+      <c r="D364" s="0">
+        <v>-3.7101359592715295</v>
+      </c>
+      <c r="E364" s="0">
+        <v>1</v>
+      </c>
+      <c r="F364" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="B365" s="0">
+        <v>96.916535030663638</v>
+      </c>
+      <c r="C365" s="0">
+        <v>21.404794641046784</v>
+      </c>
+      <c r="D365" s="0">
+        <v>-4.7143641044135407</v>
+      </c>
+      <c r="E365" s="0">
+        <v>1</v>
+      </c>
+      <c r="F365" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="B366" s="0">
+        <v>77.332752917237599</v>
+      </c>
+      <c r="C366" s="0">
+        <v>18.441258579486743</v>
+      </c>
+      <c r="D366" s="0">
+        <v>-0.88956512633168117</v>
+      </c>
+      <c r="E366" s="0">
+        <v>1</v>
+      </c>
+      <c r="F366" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="B367" s="0">
+        <v>63.716273311132866</v>
+      </c>
+      <c r="C367" s="0">
+        <v>39.923118079903546</v>
+      </c>
+      <c r="D367" s="0">
+        <v>-40.033094908159995</v>
+      </c>
+      <c r="E367" s="0">
+        <v>1</v>
+      </c>
+      <c r="F367" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="B368" s="0">
+        <v>78.705035434706446</v>
+      </c>
+      <c r="C368" s="0">
+        <v>19.729970918899792</v>
+      </c>
+      <c r="D368" s="0">
+        <v>-2.4515240673106407</v>
+      </c>
+      <c r="E368" s="0">
+        <v>1</v>
+      </c>
+      <c r="F368" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="0" t="s">
+        <v>274</v>
+      </c>
+      <c r="B369" s="0">
+        <v>94.066618832458062</v>
+      </c>
+      <c r="C369" s="0">
+        <v>21.893930117461469</v>
+      </c>
+      <c r="D369" s="0">
+        <v>-2.0782682961030914</v>
+      </c>
+      <c r="E369" s="0">
+        <v>1</v>
+      </c>
+      <c r="F369" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="0" t="s">
+        <v>275</v>
+      </c>
+      <c r="B370" s="0">
+        <v>97.003313644578327</v>
+      </c>
+      <c r="C370" s="0">
+        <v>48.999912432495549</v>
+      </c>
+      <c r="D370" s="0">
+        <v>0.29642658770896707</v>
+      </c>
+      <c r="E370" s="0">
+        <v>1</v>
+      </c>
+      <c r="F370" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="0" t="s">
+        <v>157</v>
+      </c>
+      <c r="B371" s="0">
+        <v>73.69691783831027</v>
+      </c>
+      <c r="C371" s="0">
+        <v>37.219880935689176</v>
+      </c>
+      <c r="D371" s="0">
+        <v>-0.88778237964315454</v>
+      </c>
+      <c r="E371" s="0">
+        <v>1</v>
+      </c>
+      <c r="F371" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="B372" s="0">
+        <v>102.33838419985081</v>
+      </c>
+      <c r="C372" s="0">
+        <v>24.118052698751928</v>
+      </c>
+      <c r="D372" s="0">
+        <v>1.1451624094504955</v>
+      </c>
+      <c r="E372" s="0">
+        <v>1</v>
+      </c>
+      <c r="F372" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="B373" s="0">
+        <v>81.386442185682057</v>
+      </c>
+      <c r="C373" s="0">
+        <v>41.165550636101756</v>
+      </c>
+      <c r="D373" s="0">
+        <v>-0.53113526047995052</v>
+      </c>
+      <c r="E373" s="0">
+        <v>1</v>
+      </c>
+      <c r="F373" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="0" t="s">
+        <v>158</v>
+      </c>
+      <c r="B374" s="0">
+        <v>108.17745198382238</v>
+      </c>
+      <c r="C374" s="0">
+        <v>26.326108588410008</v>
+      </c>
+      <c r="D374" s="0">
+        <v>-5.7581927137866593</v>
+      </c>
+      <c r="E374" s="0">
+        <v>1</v>
+      </c>
+      <c r="F374" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="B375" s="0">
+        <v>91.990628008568123</v>
+      </c>
+      <c r="C375" s="0">
+        <v>21.572422244415403</v>
+      </c>
+      <c r="D375" s="0">
+        <v>1.3402320524286342</v>
+      </c>
+      <c r="E375" s="0">
+        <v>1</v>
+      </c>
+      <c r="F375" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="0" t="s">
+        <v>279</v>
+      </c>
+      <c r="B376" s="0">
+        <v>8.2701063570392463</v>
+      </c>
+      <c r="C376" s="0">
+        <v>1.307773735173307</v>
+      </c>
+      <c r="D376" s="0">
+        <v>-4.4362532950866669</v>
+      </c>
+      <c r="E376" s="0">
+        <v>2</v>
+      </c>
+      <c r="F376" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="0" t="s">
+        <v>188</v>
+      </c>
+      <c r="B377" s="0">
+        <v>5.4266018009182577</v>
+      </c>
+      <c r="C377" s="0">
+        <v>3.0597009710376146</v>
+      </c>
+      <c r="D377" s="0">
+        <v>-1.8217763744364401</v>
+      </c>
+      <c r="E377" s="0">
+        <v>2</v>
+      </c>
+      <c r="F377" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="0" t="s">
+        <v>280</v>
+      </c>
+      <c r="B378" s="0">
+        <v>6.6334867618457203</v>
+      </c>
+      <c r="C378" s="0">
+        <v>1.7139419474239184</v>
+      </c>
+      <c r="D378" s="0">
+        <v>-4.0752718036307156</v>
+      </c>
+      <c r="E378" s="0">
+        <v>2</v>
+      </c>
+      <c r="F378" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="0" t="s">
+        <v>281</v>
+      </c>
+      <c r="B379" s="0">
+        <v>4.621531881874124</v>
+      </c>
+      <c r="C379" s="0">
+        <v>0.33176098087689937</v>
+      </c>
+      <c r="D379" s="0">
+        <v>-1.7893954429789436</v>
+      </c>
+      <c r="E379" s="0">
+        <v>2</v>
+      </c>
+      <c r="F379" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="B380" s="0">
+        <v>7.4927389183337674</v>
+      </c>
+      <c r="C380" s="0">
+        <v>2.021682536622841</v>
+      </c>
+      <c r="D380" s="0">
+        <v>-2.0276957776736708</v>
+      </c>
+      <c r="E380" s="0">
+        <v>2</v>
+      </c>
+      <c r="F380" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="B381" s="0">
+        <v>4.7857739454436841</v>
+      </c>
+      <c r="C381" s="0">
+        <v>1.7935662323500943</v>
+      </c>
+      <c r="D381" s="0">
+        <v>-1.8421401428034649</v>
+      </c>
+      <c r="E381" s="0">
+        <v>2</v>
+      </c>
+      <c r="F381" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="B382" s="0">
+        <v>9.214383219643091</v>
+      </c>
+      <c r="C382" s="0">
+        <v>3.1870327493791946</v>
+      </c>
+      <c r="D382" s="0">
+        <v>-6.1300529510726767</v>
+      </c>
+      <c r="E382" s="0">
+        <v>2</v>
+      </c>
+      <c r="F382" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="B383" s="0">
+        <v>6.4970106461343482</v>
+      </c>
+      <c r="C383" s="0">
+        <v>0.01181381022540693</v>
+      </c>
+      <c r="D383" s="0">
+        <v>-3.1594296925180441</v>
+      </c>
+      <c r="E383" s="0">
+        <v>2</v>
+      </c>
+      <c r="F383" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="B384" s="0">
+        <v>6.6752826544100596</v>
+      </c>
+      <c r="C384" s="0">
+        <v>3.0746806728142362</v>
+      </c>
+      <c r="D384" s="0">
+        <v>-3.7811328294808226</v>
+      </c>
+      <c r="E384" s="0">
+        <v>2</v>
+      </c>
+      <c r="F384" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="0" t="s">
+        <v>282</v>
+      </c>
+      <c r="B385" s="0">
+        <v>2.3765217158551311</v>
+      </c>
+      <c r="C385" s="0">
+        <v>0.88318028666723913</v>
+      </c>
+      <c r="D385" s="0">
+        <v>53.703752456820972</v>
+      </c>
+      <c r="E385" s="0">
+        <v>2</v>
+      </c>
+      <c r="F385" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="0" t="s">
+        <v>283</v>
+      </c>
+      <c r="B386" s="0">
+        <v>4.6348048645585322</v>
+      </c>
+      <c r="C386" s="0">
+        <v>0.8165606536986415</v>
+      </c>
+      <c r="D386" s="0">
+        <v>1.9981371907749137</v>
+      </c>
+      <c r="E386" s="0">
+        <v>2</v>
+      </c>
+      <c r="F386" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="B387" s="0">
+        <v>13.499549880713918</v>
+      </c>
+      <c r="C387" s="0">
+        <v>3.9931321726169444</v>
+      </c>
+      <c r="D387" s="0">
+        <v>-1.4906530815437271</v>
+      </c>
+      <c r="E387" s="0">
+        <v>2</v>
+      </c>
+      <c r="F387" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="B388" s="0">
+        <v>9.214383219643091</v>
+      </c>
+      <c r="C388" s="0">
+        <v>3.1870327493791946</v>
+      </c>
+      <c r="D388" s="0">
+        <v>-6.1300529510726767</v>
+      </c>
+      <c r="E388" s="0">
+        <v>2</v>
+      </c>
+      <c r="F388" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="B389" s="0">
+        <v>6.833900096596091</v>
+      </c>
+      <c r="C389" s="0">
+        <v>2.8708341865628602</v>
+      </c>
+      <c r="D389" s="0">
+        <v>-3.5711553238258538</v>
+      </c>
+      <c r="E389" s="0">
+        <v>2</v>
+      </c>
+      <c r="F389" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="B390" s="0">
+        <v>6.6752826544100596</v>
+      </c>
+      <c r="C390" s="0">
+        <v>3.0746806728142362</v>
+      </c>
+      <c r="D390" s="0">
+        <v>-3.7811328294808226</v>
+      </c>
+      <c r="E390" s="0">
+        <v>2</v>
+      </c>
+      <c r="F390" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="B391" s="0">
+        <v>7.4927389183337674</v>
+      </c>
+      <c r="C391" s="0">
+        <v>2.021682536622841</v>
+      </c>
+      <c r="D391" s="0">
+        <v>-2.0276957776736708</v>
+      </c>
+      <c r="E391" s="0">
+        <v>2</v>
+      </c>
+      <c r="F391" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="B392" s="0">
+        <v>6.4970106461343482</v>
+      </c>
+      <c r="C392" s="0">
+        <v>0.01181381022540693</v>
+      </c>
+      <c r="D392" s="0">
+        <v>-3.1594296925180441</v>
+      </c>
+      <c r="E392" s="0">
+        <v>2</v>
+      </c>
+      <c r="F392" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="B393" s="0">
+        <v>18.921993437002094</v>
+      </c>
+      <c r="C393" s="0">
+        <v>-22.323984559099721</v>
+      </c>
+      <c r="D393" s="0">
+        <v>-0.2805634334811859</v>
+      </c>
+      <c r="E393" s="0">
+        <v>2</v>
+      </c>
+      <c r="F393" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="0" t="s">
+        <v>196</v>
+      </c>
+      <c r="B394" s="0">
+        <v>2.0984039816217432</v>
+      </c>
+      <c r="C394" s="0">
+        <v>1.0956710797552147</v>
+      </c>
+      <c r="D394" s="0">
+        <v>0.37049750931736053</v>
+      </c>
+      <c r="E394" s="0">
+        <v>2</v>
+      </c>
+      <c r="F394" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="B395" s="0">
+        <v>4.7047806794401961</v>
+      </c>
+      <c r="C395" s="0">
+        <v>1.1066859665540754</v>
+      </c>
+      <c r="D395" s="0">
+        <v>-2.6127782604835281</v>
+      </c>
+      <c r="E395" s="0">
+        <v>2</v>
+      </c>
+      <c r="F395" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="0" t="s">
+        <v>284</v>
+      </c>
+      <c r="B396" s="0">
+        <v>3.1187622561720634</v>
+      </c>
+      <c r="C396" s="0">
+        <v>0.3767095925894296</v>
+      </c>
+      <c r="D396" s="0">
+        <v>1.638212111378089</v>
+      </c>
+      <c r="E396" s="0">
+        <v>2</v>
+      </c>
+      <c r="F396" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="B397" s="0">
+        <v>2.8472650913912596</v>
+      </c>
+      <c r="C397" s="0">
+        <v>1.2021415611736035</v>
+      </c>
+      <c r="D397" s="0">
+        <v>21.224727785490167</v>
+      </c>
+      <c r="E397" s="0">
+        <v>2</v>
+      </c>
+      <c r="F397" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="B398" s="0">
+        <v>6.522074341123143</v>
+      </c>
+      <c r="C398" s="0">
+        <v>1.6969508911436513</v>
+      </c>
+      <c r="D398" s="0">
+        <v>-4.4692828109746463</v>
+      </c>
+      <c r="E398" s="0">
+        <v>2</v>
+      </c>
+      <c r="F398" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B399" s="0">
+        <v>11.240201304578427</v>
+      </c>
+      <c r="C399" s="0">
+        <v>3.1213690088067043</v>
+      </c>
+      <c r="D399" s="0">
+        <v>-6.0357599153370005</v>
+      </c>
+      <c r="E399" s="0">
+        <v>2</v>
+      </c>
+      <c r="F399" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="B400" s="0">
+        <v>3.282756864213388</v>
+      </c>
+      <c r="C400" s="0">
+        <v>1.5984791711086077</v>
+      </c>
+      <c r="D400" s="0">
+        <v>-1.2789148788616316</v>
+      </c>
+      <c r="E400" s="0">
+        <v>2</v>
+      </c>
+      <c r="F400" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="B401" s="0">
+        <v>1.946456772337346</v>
+      </c>
+      <c r="C401" s="0">
+        <v>-0.60139686761133526</v>
+      </c>
+      <c r="D401" s="0">
+        <v>-1.1925282016155143</v>
+      </c>
+      <c r="E401" s="0">
+        <v>2</v>
+      </c>
+      <c r="F401" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="B402" s="0">
+        <v>2.3497193931830829</v>
+      </c>
+      <c r="C402" s="0">
+        <v>0.68748626570015947</v>
+      </c>
+      <c r="D402" s="0">
+        <v>6.0374157403501494</v>
+      </c>
+      <c r="E402" s="0">
+        <v>2</v>
+      </c>
+      <c r="F402" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="0" t="s">
+        <v>200</v>
+      </c>
+      <c r="B403" s="0">
+        <v>7.2240000756258267</v>
+      </c>
+      <c r="C403" s="0">
+        <v>1.8661270730911199</v>
+      </c>
+      <c r="D403" s="0">
+        <v>-2.1737404162515985</v>
+      </c>
+      <c r="E403" s="0">
+        <v>2</v>
+      </c>
+      <c r="F403" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="0" t="s">
+        <v>201</v>
+      </c>
+      <c r="B404" s="0">
+        <v>2.585731149431755</v>
+      </c>
+      <c r="C404" s="0">
+        <v>-0.47828414090591631</v>
+      </c>
+      <c r="D404" s="0">
+        <v>3.792588212509274</v>
+      </c>
+      <c r="E404" s="0">
+        <v>2</v>
+      </c>
+      <c r="F404" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="B405" s="0">
+        <v>1.3963124558711204</v>
+      </c>
+      <c r="C405" s="0">
+        <v>-1.0158154835728443</v>
+      </c>
+      <c r="D405" s="0">
+        <v>40.134861364021141</v>
+      </c>
+      <c r="E405" s="0">
+        <v>2</v>
+      </c>
+      <c r="F405" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="0" t="s">
+        <v>203</v>
+      </c>
+      <c r="B406" s="0">
+        <v>7.5270803620536162</v>
+      </c>
+      <c r="C406" s="0">
+        <v>-0.40752975195763891</v>
+      </c>
+      <c r="D406" s="0">
+        <v>-2.9614358528040232</v>
+      </c>
+      <c r="E406" s="0">
+        <v>2</v>
+      </c>
+      <c r="F406" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="0" t="s">
+        <v>186</v>
+      </c>
+      <c r="B407" s="0">
+        <v>6.2520676675884372</v>
+      </c>
+      <c r="C407" s="0">
+        <v>2.3742342184716581</v>
+      </c>
+      <c r="D407" s="0">
+        <v>-2.3099475655759263</v>
+      </c>
+      <c r="E407" s="0">
+        <v>2</v>
+      </c>
+      <c r="F407" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="0" t="s">
+        <v>287</v>
+      </c>
+      <c r="B408" s="0">
+        <v>5.4268237729763751</v>
+      </c>
+      <c r="C408" s="0">
+        <v>1.5856408315013504</v>
+      </c>
+      <c r="D408" s="0">
+        <v>-1.0693611341951881</v>
+      </c>
+      <c r="E408" s="0">
+        <v>2</v>
+      </c>
+      <c r="F408" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="B409" s="0">
+        <v>7.6344671795518622</v>
+      </c>
+      <c r="C409" s="0">
+        <v>1.9347849488617204</v>
+      </c>
+      <c r="D409" s="0">
+        <v>-5.175353829560537</v>
+      </c>
+      <c r="E409" s="0">
+        <v>2</v>
+      </c>
+      <c r="F409" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="B410" s="0">
+        <v>7.0411254478559586</v>
+      </c>
+      <c r="C410" s="0">
+        <v>2.7814274758245099</v>
+      </c>
+      <c r="D410" s="0">
+        <v>8.3614141935937418</v>
+      </c>
+      <c r="E410" s="0">
+        <v>2</v>
+      </c>
+      <c r="F410" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="0" t="s">
+        <v>288</v>
+      </c>
+      <c r="B411" s="0">
+        <v>6.2158623455681594</v>
+      </c>
+      <c r="C411" s="0">
+        <v>0.84354669420795214</v>
+      </c>
+      <c r="D411" s="0">
+        <v>-3.1414644627167321</v>
+      </c>
+      <c r="E411" s="0">
+        <v>2</v>
+      </c>
+      <c r="F411" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="B412" s="0">
+        <v>4.2425378105432801</v>
+      </c>
+      <c r="C412" s="0">
+        <v>1.9925052986193998</v>
+      </c>
+      <c r="D412" s="0">
+        <v>0.29835539829032126</v>
+      </c>
+      <c r="E412" s="0">
+        <v>2</v>
+      </c>
+      <c r="F412" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="0" t="s">
+        <v>290</v>
+      </c>
+      <c r="B413" s="0">
+        <v>2.2733103261838807</v>
+      </c>
+      <c r="C413" s="0">
+        <v>-1.1769193475017259</v>
+      </c>
+      <c r="D413" s="0">
+        <v>3.256299861199381</v>
+      </c>
+      <c r="E413" s="0">
+        <v>2</v>
+      </c>
+      <c r="F413" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="0" t="s">
+        <v>291</v>
+      </c>
+      <c r="B414" s="0">
+        <v>10.04043960615877</v>
+      </c>
+      <c r="C414" s="0">
+        <v>2.9963055998192796</v>
+      </c>
+      <c r="D414" s="0">
+        <v>-1.5794496551609538</v>
+      </c>
+      <c r="E414" s="0">
+        <v>2</v>
+      </c>
+      <c r="F414" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="0" t="s">
+        <v>292</v>
+      </c>
+      <c r="B415" s="0">
+        <v>8.0774208448492519</v>
+      </c>
+      <c r="C415" s="0">
+        <v>4.3784322965849078</v>
+      </c>
+      <c r="D415" s="0">
+        <v>-3.9006457105625252</v>
+      </c>
+      <c r="E415" s="0">
+        <v>2</v>
+      </c>
+      <c r="F415" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="0" t="s">
+        <v>293</v>
+      </c>
+      <c r="B416" s="0">
+        <v>5.1129120897962173</v>
+      </c>
+      <c r="C416" s="0">
+        <v>0.6419245955252787</v>
+      </c>
+      <c r="D416" s="0">
+        <v>-2.3803902868186393</v>
+      </c>
+      <c r="E416" s="0">
+        <v>2</v>
+      </c>
+      <c r="F416" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="0" t="s">
+        <v>187</v>
+      </c>
+      <c r="B417" s="0">
+        <v>9.0776909107140238</v>
+      </c>
+      <c r="C417" s="0">
+        <v>-1.2063529199223244</v>
+      </c>
+      <c r="D417" s="0">
+        <v>1.7098541264627163</v>
+      </c>
+      <c r="E417" s="0">
+        <v>2</v>
+      </c>
+      <c r="F417" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="0" t="s">
+        <v>188</v>
+      </c>
+      <c r="B418" s="0">
+        <v>5.4266018009182577</v>
+      </c>
+      <c r="C418" s="0">
+        <v>3.0597009710376146</v>
+      </c>
+      <c r="D418" s="0">
+        <v>-1.8217763744364401</v>
+      </c>
+      <c r="E418" s="0">
+        <v>2</v>
+      </c>
+      <c r="F418" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="B419" s="0">
+        <v>13.341912326559124</v>
+      </c>
+      <c r="C419" s="0">
+        <v>5.0731972244290526</v>
+      </c>
+      <c r="D419" s="0">
+        <v>0.028334674279826267</v>
+      </c>
+      <c r="E419" s="0">
+        <v>2</v>
+      </c>
+      <c r="F419" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="B420" s="0">
+        <v>6.2543816500894378</v>
+      </c>
+      <c r="C420" s="0">
+        <v>1.1031189395917109</v>
+      </c>
+      <c r="D420" s="0">
+        <v>-2.5388105003269645</v>
+      </c>
+      <c r="E420" s="0">
+        <v>2</v>
+      </c>
+      <c r="F420" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="B421" s="0">
+        <v>7.4927389183337674</v>
+      </c>
+      <c r="C421" s="0">
+        <v>2.021682536622841</v>
+      </c>
+      <c r="D421" s="0">
+        <v>-2.0276957776736708</v>
+      </c>
+      <c r="E421" s="0">
+        <v>2</v>
+      </c>
+      <c r="F421" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="B422" s="0">
+        <v>6.4970106461343482</v>
+      </c>
+      <c r="C422" s="0">
+        <v>0.01181381022540693</v>
+      </c>
+      <c r="D422" s="0">
+        <v>-3.1594296925180441</v>
+      </c>
+      <c r="E422" s="0">
+        <v>2</v>
+      </c>
+      <c r="F422" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="0" t="s">
+        <v>195</v>
+      </c>
+      <c r="B423" s="0">
+        <v>32.767838194293788</v>
+      </c>
+      <c r="C423" s="0">
+        <v>15.281708565615357</v>
+      </c>
+      <c r="D423" s="0">
+        <v>-1.3022100231529989</v>
+      </c>
+      <c r="E423" s="0">
+        <v>2</v>
+      </c>
+      <c r="F423" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="0" t="s">
+        <v>294</v>
+      </c>
+      <c r="B424" s="0">
+        <v>9.3223740186294464</v>
+      </c>
+      <c r="C424" s="0">
+        <v>3.9696076014565325</v>
+      </c>
+      <c r="D424" s="0">
+        <v>-4.5798999668765834</v>
+      </c>
+      <c r="E424" s="0">
+        <v>2</v>
+      </c>
+      <c r="F424" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="0" t="s">
+        <v>197</v>
+      </c>
+      <c r="B425" s="0">
+        <v>4.9512596714185797</v>
+      </c>
+      <c r="C425" s="0">
+        <v>1.6544778686106518</v>
+      </c>
+      <c r="D425" s="0">
+        <v>-3.7185443653397563</v>
+      </c>
+      <c r="E425" s="0">
+        <v>2</v>
+      </c>
+      <c r="F425" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="0" t="s">
+        <v>295</v>
+      </c>
+      <c r="B426" s="0">
+        <v>3.2871859858485841</v>
+      </c>
+      <c r="C426" s="0">
+        <v>0.35929857138327564</v>
+      </c>
+      <c r="D426" s="0">
+        <v>-2.5252779514920802</v>
+      </c>
+      <c r="E426" s="0">
+        <v>2</v>
+      </c>
+      <c r="F426" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="0" t="s">
+        <v>198</v>
+      </c>
+      <c r="B427" s="0">
+        <v>21.831929216436237</v>
+      </c>
+      <c r="C427" s="0">
+        <v>6.9723346597346332</v>
+      </c>
+      <c r="D427" s="0">
+        <v>-0.78406058230535314</v>
+      </c>
+      <c r="E427" s="0">
+        <v>2</v>
+      </c>
+      <c r="F427" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="0" t="s">
+        <v>296</v>
+      </c>
+      <c r="B428" s="0">
+        <v>10.387282525681933</v>
+      </c>
+      <c r="C428" s="0">
+        <v>1.7565126946767691</v>
+      </c>
+      <c r="D428" s="0">
+        <v>-3.1800358045769181</v>
+      </c>
+      <c r="E428" s="0">
+        <v>2</v>
+      </c>
+      <c r="F428" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="0" t="s">
+        <v>297</v>
+      </c>
+      <c r="B429" s="0">
+        <v>3.6583305166608873</v>
+      </c>
+      <c r="C429" s="0">
+        <v>-0.07954605213494316</v>
+      </c>
+      <c r="D429" s="0">
+        <v>0.30572612692939305</v>
+      </c>
+      <c r="E429" s="0">
+        <v>2</v>
+      </c>
+      <c r="F429" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="B430" s="0">
+        <v>3.1298276767437834</v>
+      </c>
+      <c r="C430" s="0">
+        <v>1.0399565136112738</v>
+      </c>
+      <c r="D430" s="0">
+        <v>-1.8422661306103685</v>
+      </c>
+      <c r="E430" s="0">
+        <v>2</v>
+      </c>
+      <c r="F430" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="0" t="s">
+        <v>298</v>
+      </c>
+      <c r="B431" s="0">
+        <v>4.3617598004460216</v>
+      </c>
+      <c r="C431" s="0">
+        <v>0.99247687275500796</v>
+      </c>
+      <c r="D431" s="0">
+        <v>26.594878238497074</v>
+      </c>
+      <c r="E431" s="0">
+        <v>2</v>
+      </c>
+      <c r="F431" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="B432" s="0">
+        <v>13.499549880713918</v>
+      </c>
+      <c r="C432" s="0">
+        <v>3.9931321726169444</v>
+      </c>
+      <c r="D432" s="0">
+        <v>-1.4906530815437271</v>
+      </c>
+      <c r="E432" s="0">
+        <v>2</v>
+      </c>
+      <c r="F432" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="B433" s="0">
+        <v>1.8323412776035861</v>
+      </c>
+      <c r="C433" s="0">
+        <v>0.76763743124178252</v>
+      </c>
+      <c r="D433" s="0">
+        <v>25.577867506393368</v>
+      </c>
+      <c r="E433" s="0">
+        <v>2</v>
+      </c>
+      <c r="F433" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="B434" s="0">
+        <v>9.3453225087404306</v>
+      </c>
+      <c r="C434" s="0">
+        <v>1.6565295963192259</v>
+      </c>
+      <c r="D434" s="0">
+        <v>-2.0455689180406704</v>
+      </c>
+      <c r="E434" s="0">
+        <v>2</v>
+      </c>
+      <c r="F434" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="0" t="s">
+        <v>299</v>
+      </c>
+      <c r="B435" s="0">
+        <v>1.1893400049145939</v>
+      </c>
+      <c r="C435" s="0">
+        <v>0.96708773344648535</v>
+      </c>
+      <c r="D435" s="0">
+        <v>3.1945274815031595</v>
+      </c>
+      <c r="E435" s="0">
+        <v>2</v>
+      </c>
+      <c r="F435" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="0" t="s">
+        <v>300</v>
+      </c>
+      <c r="B436" s="0">
+        <v>3.2335057667185043</v>
+      </c>
+      <c r="C436" s="0">
+        <v>1.0301954094573245</v>
+      </c>
+      <c r="D436" s="0">
+        <v>-2.1920126327896168</v>
+      </c>
+      <c r="E436" s="0">
+        <v>2</v>
+      </c>
+      <c r="F436" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="0" t="s">
+        <v>301</v>
+      </c>
+      <c r="B437" s="0">
+        <v>0.80321721364575072</v>
+      </c>
+      <c r="C437" s="0">
+        <v>-0.12362630905567662</v>
+      </c>
+      <c r="D437" s="0">
+        <v>-0.96117049079253958</v>
+      </c>
+      <c r="E437" s="0">
+        <v>2</v>
+      </c>
+      <c r="F437" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="0" t="s">
+        <v>302</v>
+      </c>
+      <c r="B438" s="0">
+        <v>5.4794577848341106</v>
+      </c>
+      <c r="C438" s="0">
+        <v>1.9290685283245705</v>
+      </c>
+      <c r="D438" s="0">
+        <v>-2.2625185333660975</v>
+      </c>
+      <c r="E438" s="0">
+        <v>2</v>
+      </c>
+      <c r="F438" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="0" t="s">
+        <v>303</v>
+      </c>
+      <c r="B439" s="0">
+        <v>4.5779744018213773</v>
+      </c>
+      <c r="C439" s="0">
+        <v>2.0480729670787645</v>
+      </c>
+      <c r="D439" s="0">
+        <v>-1.5983312450898124</v>
+      </c>
+      <c r="E439" s="0">
+        <v>2</v>
+      </c>
+      <c r="F439" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="0" t="s">
+        <v>304</v>
+      </c>
+      <c r="B440" s="0">
+        <v>4.9533340475949936</v>
+      </c>
+      <c r="C440" s="0">
+        <v>0.72054392877949791</v>
+      </c>
+      <c r="D440" s="0">
+        <v>-1.1154711803403372</v>
+      </c>
+      <c r="E440" s="0">
+        <v>2</v>
+      </c>
+      <c r="F440" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="0" t="s">
+        <v>305</v>
+      </c>
+      <c r="B441" s="0">
+        <v>6.0015586305010657</v>
+      </c>
+      <c r="C441" s="0">
+        <v>2.273065827406108</v>
+      </c>
+      <c r="D441" s="0">
+        <v>0.062241076884322281</v>
+      </c>
+      <c r="E441" s="0">
+        <v>2</v>
+      </c>
+      <c r="F441" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="0" t="s">
+        <v>306</v>
+      </c>
+      <c r="B442" s="0">
+        <v>10.523653363078278</v>
+      </c>
+      <c r="C442" s="0">
+        <v>2.2721275568034063</v>
+      </c>
+      <c r="D442" s="0">
+        <v>0.02511835717351537</v>
+      </c>
+      <c r="E442" s="0">
+        <v>2</v>
+      </c>
+      <c r="F442" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="0" t="s">
+        <v>307</v>
+      </c>
+      <c r="B443" s="0">
+        <v>4.3440595574115601</v>
+      </c>
+      <c r="C443" s="0">
+        <v>-0.87635607000929672</v>
+      </c>
+      <c r="D443" s="0">
+        <v>-0.087020372189712605</v>
+      </c>
+      <c r="E443" s="0">
+        <v>2</v>
+      </c>
+      <c r="F443" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="0" t="s">
+        <v>302</v>
+      </c>
+      <c r="B444" s="0">
+        <v>5.4794577848341106</v>
+      </c>
+      <c r="C444" s="0">
+        <v>1.9290685283245705</v>
+      </c>
+      <c r="D444" s="0">
+        <v>-2.2625185333660975</v>
+      </c>
+      <c r="E444" s="0">
+        <v>2</v>
+      </c>
+      <c r="F444" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="0" t="s">
+        <v>232</v>
+      </c>
+      <c r="B445" s="0">
+        <v>0.98978398629640374</v>
+      </c>
+      <c r="C445" s="0">
+        <v>1.2851847352364598</v>
+      </c>
+      <c r="D445" s="0">
+        <v>22.424898138116387</v>
+      </c>
+      <c r="E445" s="0">
+        <v>2</v>
+      </c>
+      <c r="F445" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="0" t="s">
+        <v>235</v>
+      </c>
+      <c r="B446" s="0">
+        <v>10.18495462549707</v>
+      </c>
+      <c r="C446" s="0">
+        <v>5.3554491449092936</v>
+      </c>
+      <c r="D446" s="0">
+        <v>-0.85278416763645182</v>
+      </c>
+      <c r="E446" s="0">
+        <v>2</v>
+      </c>
+      <c r="F446" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="0" t="s">
+        <v>236</v>
+      </c>
+      <c r="B447" s="0">
+        <v>4.7386322556024805</v>
+      </c>
+      <c r="C447" s="0">
+        <v>1.2814419779956836</v>
+      </c>
+      <c r="D447" s="0">
+        <v>-1.5728295664705525</v>
+      </c>
+      <c r="E447" s="0">
+        <v>2</v>
+      </c>
+      <c r="F447" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="0" t="s">
+        <v>231</v>
+      </c>
+      <c r="B448" s="0">
+        <v>0.68013589251628381</v>
+      </c>
+      <c r="C448" s="0">
+        <v>-1.0206707238291433</v>
+      </c>
+      <c r="D448" s="0">
+        <v>22.533627221502137</v>
+      </c>
+      <c r="E448" s="0">
+        <v>2</v>
+      </c>
+      <c r="F448" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="0" t="s">
+        <v>308</v>
+      </c>
+      <c r="B449" s="0">
+        <v>2.215040288747534</v>
+      </c>
+      <c r="C449" s="0">
+        <v>-0.17935084715453672</v>
+      </c>
+      <c r="D449" s="0">
+        <v>0.45711565523414222</v>
+      </c>
+      <c r="E449" s="0">
+        <v>2</v>
+      </c>
+      <c r="F449" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="0" t="s">
+        <v>308</v>
+      </c>
+      <c r="B450" s="0">
+        <v>2.215040288747534</v>
+      </c>
+      <c r="C450" s="0">
+        <v>-0.17935084715453672</v>
+      </c>
+      <c r="D450" s="0">
+        <v>0.45711565523414222</v>
+      </c>
+      <c r="E450" s="0">
+        <v>2</v>
+      </c>
+      <c r="F450" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="B451" s="0">
+        <v>6.2202245608802329</v>
+      </c>
+      <c r="C451" s="0">
+        <v>1.8041524844724541</v>
+      </c>
+      <c r="D451" s="0">
+        <v>-3.051434063886922</v>
+      </c>
+      <c r="E451" s="0">
+        <v>2</v>
+      </c>
+      <c r="F451" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="B452" s="0">
+        <v>16.126746961029742</v>
+      </c>
+      <c r="C452" s="0">
+        <v>4.2628207731988441</v>
+      </c>
+      <c r="D452" s="0">
+        <v>-2.7001261330900812</v>
+      </c>
+      <c r="E452" s="0">
+        <v>2</v>
+      </c>
+      <c r="F452" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="0" t="s">
+        <v>309</v>
+      </c>
+      <c r="B453" s="0">
+        <v>4.6984478535647556</v>
+      </c>
+      <c r="C453" s="0">
+        <v>0.95567012481363489</v>
+      </c>
+      <c r="D453" s="0">
+        <v>-0.63811440408251563</v>
+      </c>
+      <c r="E453" s="0">
+        <v>2</v>
+      </c>
+      <c r="F453" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="0" t="s">
+        <v>198</v>
+      </c>
+      <c r="B454" s="0">
+        <v>16.508478737062109</v>
+      </c>
+      <c r="C454" s="0">
+        <v>3.9131771613111321</v>
+      </c>
+      <c r="D454" s="0">
+        <v>-3.5142391626068878</v>
+      </c>
+      <c r="E454" s="0">
+        <v>2</v>
+      </c>
+      <c r="F454" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="0" t="s">
+        <v>310</v>
+      </c>
+      <c r="B455" s="0">
+        <v>12.309101580077709</v>
+      </c>
+      <c r="C455" s="0">
+        <v>1.6565093070485821</v>
+      </c>
+      <c r="D455" s="0">
+        <v>-4.7772509770110769</v>
+      </c>
+      <c r="E455" s="0">
+        <v>2</v>
+      </c>
+      <c r="F455" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B456" s="0">
+        <v>8.1279392648566393</v>
+      </c>
+      <c r="C456" s="0">
+        <v>2.3323900770164681</v>
+      </c>
+      <c r="D456" s="0">
+        <v>-2.6578585767575484</v>
+      </c>
+      <c r="E456" s="0">
+        <v>2</v>
+      </c>
+      <c r="F456" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="0" t="s">
+        <v>311</v>
+      </c>
+      <c r="B457" s="0">
+        <v>5.7887722057004654</v>
+      </c>
+      <c r="C457" s="0">
+        <v>2.7338043959712497</v>
+      </c>
+      <c r="D457" s="0">
+        <v>5.6573301937222293</v>
+      </c>
+      <c r="E457" s="0">
+        <v>2</v>
+      </c>
+      <c r="F457" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="0" t="s">
+        <v>307</v>
+      </c>
+      <c r="B458" s="0">
+        <v>0.049100269631904919</v>
+      </c>
+      <c r="C458" s="0">
+        <v>0.21655088490176103</v>
+      </c>
+      <c r="D458" s="0">
+        <v>17.72103978765227</v>
+      </c>
+      <c r="E458" s="0">
+        <v>2</v>
+      </c>
+      <c r="F458" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="B459" s="0">
+        <v>17.633523128270312</v>
+      </c>
+      <c r="C459" s="0">
+        <v>5.4703257703352701</v>
+      </c>
+      <c r="D459" s="0">
+        <v>-2.6538121601390472</v>
+      </c>
+      <c r="E459" s="0">
+        <v>2</v>
+      </c>
+      <c r="F459" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="0" t="s">
+        <v>312</v>
+      </c>
+      <c r="B460" s="0">
+        <v>26.667740745480401</v>
+      </c>
+      <c r="C460" s="0">
+        <v>6.7158632012859796</v>
+      </c>
+      <c r="D460" s="0">
+        <v>-2.5695969601462569</v>
+      </c>
+      <c r="E460" s="0">
+        <v>2</v>
+      </c>
+      <c r="F460" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="B461" s="0">
+        <v>7.5831800090088182</v>
+      </c>
+      <c r="C461" s="0">
+        <v>2.1270648794493123</v>
+      </c>
+      <c r="D461" s="0">
+        <v>-1.9848576166978864</v>
+      </c>
+      <c r="E461" s="0">
+        <v>2</v>
+      </c>
+      <c r="F461" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="0" t="s">
+        <v>311</v>
+      </c>
+      <c r="B462" s="0">
+        <v>7.8137300202090785</v>
+      </c>
+      <c r="C462" s="0">
+        <v>2.0564485170994415</v>
+      </c>
+      <c r="D462" s="0">
+        <v>3.3563121166639909</v>
+      </c>
+      <c r="E462" s="0">
+        <v>2</v>
+      </c>
+      <c r="F462" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="0" t="s">
+        <v>167</v>
+      </c>
+      <c r="B463" s="0">
+        <v>11.479242963510428</v>
+      </c>
+      <c r="C463" s="0">
+        <v>6.3854192149922078</v>
+      </c>
+      <c r="D463" s="0">
+        <v>-2.8963075009136401</v>
+      </c>
+      <c r="E463" s="0">
+        <v>2</v>
+      </c>
+      <c r="F463" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="0" t="s">
+        <v>313</v>
+      </c>
+      <c r="B464" s="0">
+        <v>5.6116558407127046</v>
+      </c>
+      <c r="C464" s="0">
+        <v>0.17311996479385658</v>
+      </c>
+      <c r="D464" s="0">
+        <v>-2.2514668108180151</v>
+      </c>
+      <c r="E464" s="0">
+        <v>2</v>
+      </c>
+      <c r="F464" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="B465" s="0">
+        <v>7.3755157813373673</v>
+      </c>
+      <c r="C465" s="0">
+        <v>2.4989817478501388</v>
+      </c>
+      <c r="D465" s="0">
+        <v>2.5283926400134762</v>
+      </c>
+      <c r="E465" s="0">
+        <v>2</v>
+      </c>
+      <c r="F465" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="0" t="s">
+        <v>314</v>
+      </c>
+      <c r="B466" s="0">
+        <v>4.5352745647654888</v>
+      </c>
+      <c r="C466" s="0">
+        <v>1.4734260617546169</v>
+      </c>
+      <c r="D466" s="0">
+        <v>-2.5053238656568926</v>
+      </c>
+      <c r="E466" s="0">
+        <v>2</v>
+      </c>
+      <c r="F466" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="B467" s="0">
+        <v>5.242708589112258</v>
+      </c>
+      <c r="C467" s="0">
+        <v>1.8555499972651828</v>
+      </c>
+      <c r="D467" s="0">
+        <v>-2.9667601421467027</v>
+      </c>
+      <c r="E467" s="0">
+        <v>2</v>
+      </c>
+      <c r="F467" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="B468" s="0">
+        <v>4.4676502824473996</v>
+      </c>
+      <c r="C468" s="0">
+        <v>1.1258105850084366</v>
+      </c>
+      <c r="D468" s="0">
+        <v>-3.3103245588040751</v>
+      </c>
+      <c r="E468" s="0">
+        <v>2</v>
+      </c>
+      <c r="F468" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="0" t="s">
+        <v>317</v>
+      </c>
+      <c r="B469" s="0">
+        <v>15.67438579923243</v>
+      </c>
+      <c r="C469" s="0">
+        <v>6.1895299028702393</v>
+      </c>
+      <c r="D469" s="0">
+        <v>-3.314076616445925</v>
+      </c>
+      <c r="E469" s="0">
+        <v>2</v>
+      </c>
+      <c r="F469" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="0" t="s">
+        <v>318</v>
+      </c>
+      <c r="B470" s="0">
+        <v>6.5462865642932639</v>
+      </c>
+      <c r="C470" s="0">
+        <v>1.3423865935693706</v>
+      </c>
+      <c r="D470" s="0">
+        <v>-2.4034158731058328</v>
+      </c>
+      <c r="E470" s="0">
+        <v>2</v>
+      </c>
+      <c r="F470" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="0" t="s">
+        <v>198</v>
+      </c>
+      <c r="B471" s="0">
+        <v>16.508478737062109</v>
+      </c>
+      <c r="C471" s="0">
+        <v>3.9131771613111321</v>
+      </c>
+      <c r="D471" s="0">
+        <v>-3.5142391626068878</v>
+      </c>
+      <c r="E471" s="0">
+        <v>2</v>
+      </c>
+      <c r="F471" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="0" t="s">
+        <v>319</v>
+      </c>
+      <c r="B472" s="0">
+        <v>4.5206381852988233</v>
+      </c>
+      <c r="C472" s="0">
+        <v>1.8761694896623637</v>
+      </c>
+      <c r="D472" s="0">
+        <v>3.2831578340352823</v>
+      </c>
+      <c r="E472" s="0">
+        <v>2</v>
+      </c>
+      <c r="F472" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="B473" s="0">
+        <v>3.1390632626666943</v>
+      </c>
+      <c r="C473" s="0">
+        <v>0.7710870072282433</v>
+      </c>
+      <c r="D473" s="0">
+        <v>2.0991862955656022</v>
+      </c>
+      <c r="E473" s="0">
+        <v>2</v>
+      </c>
+      <c r="F473" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="0" t="s">
+        <v>320</v>
+      </c>
+      <c r="B474" s="0">
+        <v>5.3452257271393675</v>
+      </c>
+      <c r="C474" s="0">
+        <v>2.4077340482562777</v>
+      </c>
+      <c r="D474" s="0">
+        <v>1.4159292178118148</v>
+      </c>
+      <c r="E474" s="0">
+        <v>2</v>
+      </c>
+      <c r="F474" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="B475" s="0">
+        <v>0.54997939376639993</v>
+      </c>
+      <c r="C475" s="0">
+        <v>0.49641221884552617</v>
+      </c>
+      <c r="D475" s="0">
+        <v>7.7303817416418683</v>
+      </c>
+      <c r="E475" s="0">
+        <v>2</v>
+      </c>
+      <c r="F475" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="0" t="s">
+        <v>321</v>
+      </c>
+      <c r="B476" s="0">
+        <v>0.54997939376639993</v>
+      </c>
+      <c r="C476" s="0">
+        <v>0.49641221884552617</v>
+      </c>
+      <c r="D476" s="0">
+        <v>7.7303817416418683</v>
+      </c>
+      <c r="E476" s="0">
+        <v>2</v>
+      </c>
+      <c r="F476" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="0" t="s">
+        <v>218</v>
+      </c>
+      <c r="B477" s="0">
+        <v>10.80667091883115</v>
+      </c>
+      <c r="C477" s="0">
+        <v>6.1595202456862577</v>
+      </c>
+      <c r="D477" s="0">
+        <v>-1.3604687519461289</v>
+      </c>
+      <c r="E477" s="0">
+        <v>2</v>
+      </c>
+      <c r="F477" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="B478" s="0">
+        <v>0.54997939376639993</v>
+      </c>
+      <c r="C478" s="0">
+        <v>0.49641221884552617</v>
+      </c>
+      <c r="D478" s="0">
+        <v>7.7303817416418683</v>
+      </c>
+      <c r="E478" s="0">
+        <v>2</v>
+      </c>
+      <c r="F478" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="0" t="s">
+        <v>321</v>
+      </c>
+      <c r="B479" s="0">
+        <v>0.54997939376639993</v>
+      </c>
+      <c r="C479" s="0">
+        <v>0.49641221884552617</v>
+      </c>
+      <c r="D479" s="0">
+        <v>7.7303817416418683</v>
+      </c>
+      <c r="E479" s="0">
+        <v>2</v>
+      </c>
+      <c r="F479" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="0" t="s">
+        <v>218</v>
+      </c>
+      <c r="B480" s="0">
+        <v>10.80667091883115</v>
+      </c>
+      <c r="C480" s="0">
+        <v>6.1595202456862577</v>
+      </c>
+      <c r="D480" s="0">
+        <v>-1.3604687519461289</v>
+      </c>
+      <c r="E480" s="0">
+        <v>2</v>
+      </c>
+      <c r="F480" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="B481" s="0">
+        <v>0.54997939376639993</v>
+      </c>
+      <c r="C481" s="0">
+        <v>0.49641221884552617</v>
+      </c>
+      <c r="D481" s="0">
+        <v>7.7303817416418683</v>
+      </c>
+      <c r="E481" s="0">
+        <v>2</v>
+      </c>
+      <c r="F481" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B482" s="0">
+        <v>2.5499919158514683</v>
+      </c>
+      <c r="C482" s="0">
+        <v>0.14633691902204796</v>
+      </c>
+      <c r="D482" s="0">
+        <v>-1.5910895336416191</v>
+      </c>
+      <c r="E482" s="0">
+        <v>2</v>
+      </c>
+      <c r="F482" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="0" t="s">
+        <v>322</v>
+      </c>
+      <c r="B483" s="0">
+        <v>0.54997939376639993</v>
+      </c>
+      <c r="C483" s="0">
+        <v>0.49641221884552617</v>
+      </c>
+      <c r="D483" s="0">
+        <v>7.7303817416418683</v>
+      </c>
+      <c r="E483" s="0">
+        <v>2</v>
+      </c>
+      <c r="F483" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="B484" s="0">
+        <v>3.5074336736909126</v>
+      </c>
+      <c r="C484" s="0">
+        <v>1.0000175739394035</v>
+      </c>
+      <c r="D484" s="0">
+        <v>13.038680079008026</v>
+      </c>
+      <c r="E484" s="0">
+        <v>2</v>
+      </c>
+      <c r="F484" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="0" t="s">
+        <v>323</v>
+      </c>
+      <c r="B485" s="0">
+        <v>1.6662950701403443</v>
+      </c>
+      <c r="C485" s="0">
+        <v>0.74629180950290552</v>
+      </c>
+      <c r="D485" s="0">
+        <v>-0.75158674358065769</v>
+      </c>
+      <c r="E485" s="0">
+        <v>2</v>
+      </c>
+      <c r="F485" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="B486" s="0">
+        <v>3.1390632626666943</v>
+      </c>
+      <c r="C486" s="0">
+        <v>0.7710870072282433</v>
+      </c>
+      <c r="D486" s="0">
+        <v>2.0991862955656022</v>
+      </c>
+      <c r="E486" s="0">
+        <v>2</v>
+      </c>
+      <c r="F486" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="B487" s="0">
+        <v>0.54997939376639993</v>
+      </c>
+      <c r="C487" s="0">
+        <v>0.49641221884552617</v>
+      </c>
+      <c r="D487" s="0">
+        <v>7.7303817416418683</v>
+      </c>
+      <c r="E487" s="0">
+        <v>2</v>
+      </c>
+      <c r="F487" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B488" s="0">
+        <v>2.5499919158514683</v>
+      </c>
+      <c r="C488" s="0">
+        <v>0.14633691902204796</v>
+      </c>
+      <c r="D488" s="0">
+        <v>-1.5910895336416191</v>
+      </c>
+      <c r="E488" s="0">
+        <v>2</v>
+      </c>
+      <c r="F488" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="0" t="s">
+        <v>322</v>
+      </c>
+      <c r="B489" s="0">
+        <v>0.54997939376639993</v>
+      </c>
+      <c r="C489" s="0">
+        <v>0.49641221884552617</v>
+      </c>
+      <c r="D489" s="0">
+        <v>7.7303817416418683</v>
+      </c>
+      <c r="E489" s="0">
+        <v>2</v>
+      </c>
+      <c r="F489" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="B490" s="0">
+        <v>6.6023908514243841</v>
+      </c>
+      <c r="C490" s="0">
+        <v>1.0152602658884378</v>
+      </c>
+      <c r="D490" s="0">
+        <v>-4.4050770684156761</v>
+      </c>
+      <c r="E490" s="0">
+        <v>2</v>
+      </c>
+      <c r="F490" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="B491" s="0">
+        <v>12.002236976766824</v>
+      </c>
+      <c r="C491" s="0">
+        <v>3.2475251362023068</v>
+      </c>
+      <c r="D491" s="0">
+        <v>-1.3790330268120428</v>
+      </c>
+      <c r="E491" s="0">
+        <v>2</v>
+      </c>
+      <c r="F491" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="0" t="s">
+        <v>166</v>
+      </c>
+      <c r="B492" s="0">
+        <v>6.5028043046809261</v>
+      </c>
+      <c r="C492" s="0">
+        <v>3.0314329615665794</v>
+      </c>
+      <c r="D492" s="0">
+        <v>-4.7218776945131467</v>
+      </c>
+      <c r="E492" s="0">
+        <v>2</v>
+      </c>
+      <c r="F492" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="0" t="s">
+        <v>324</v>
+      </c>
+      <c r="B493" s="0">
+        <v>5.3293261946269528</v>
+      </c>
+      <c r="C493" s="0">
+        <v>2.6292228712818204</v>
+      </c>
+      <c r="D493" s="0">
+        <v>-3.253653533998941</v>
+      </c>
+      <c r="E493" s="0">
+        <v>2</v>
+      </c>
+      <c r="F493" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="0" t="s">
+        <v>325</v>
+      </c>
+      <c r="B494" s="0">
+        <v>12.968413061167395</v>
+      </c>
+      <c r="C494" s="0">
+        <v>3.804181641429301</v>
+      </c>
+      <c r="D494" s="0">
+        <v>-9.484594969494978</v>
+      </c>
+      <c r="E494" s="0">
+        <v>2</v>
+      </c>
+      <c r="F494" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="0" t="s">
+        <v>314</v>
+      </c>
+      <c r="B495" s="0">
+        <v>4.8350769482874449</v>
+      </c>
+      <c r="C495" s="0">
+        <v>0.33780116011729344</v>
+      </c>
+      <c r="D495" s="0">
+        <v>-2.3142970774911777</v>
+      </c>
+      <c r="E495" s="0">
+        <v>2</v>
+      </c>
+      <c r="F495" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="0" t="s">
+        <v>326</v>
+      </c>
+      <c r="B496" s="0">
+        <v>17.493009140578859</v>
+      </c>
+      <c r="C496" s="0">
+        <v>5.828388548288741</v>
+      </c>
+      <c r="D496" s="0">
+        <v>-3.6946275618053792</v>
+      </c>
+      <c r="E496" s="0">
+        <v>2</v>
+      </c>
+      <c r="F496" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="0" t="s">
+        <v>319</v>
+      </c>
+      <c r="B497" s="0">
+        <v>4.9480978520294236</v>
+      </c>
+      <c r="C497" s="0">
+        <v>1.9817366849947737</v>
+      </c>
+      <c r="D497" s="0">
+        <v>1.5132586528381755</v>
+      </c>
+      <c r="E497" s="0">
+        <v>2</v>
+      </c>
+      <c r="F497" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="0" t="s">
+        <v>327</v>
+      </c>
+      <c r="B498" s="0">
+        <v>11.308595032189135</v>
+      </c>
+      <c r="C498" s="0">
+        <v>2.8562001019711634</v>
+      </c>
+      <c r="D498" s="0">
+        <v>-0.027542449587929341</v>
+      </c>
+      <c r="E498" s="0">
+        <v>2</v>
+      </c>
+      <c r="F498" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="0" t="s">
+        <v>328</v>
+      </c>
+      <c r="B499" s="0">
+        <v>1.0785520903213923</v>
+      </c>
+      <c r="C499" s="0">
+        <v>-1.6633401522650608</v>
+      </c>
+      <c r="D499" s="0">
+        <v>2.5719567025696488</v>
+      </c>
+      <c r="E499" s="0">
+        <v>2</v>
+      </c>
+      <c r="F499" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="0" t="s">
+        <v>291</v>
+      </c>
+      <c r="B500" s="0">
+        <v>3.2245169973284473</v>
+      </c>
+      <c r="C500" s="0">
+        <v>0.31837361965425776</v>
+      </c>
+      <c r="D500" s="0">
+        <v>-1.7708425091900388</v>
+      </c>
+      <c r="E500" s="0">
+        <v>2</v>
+      </c>
+      <c r="F500" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="0" t="s">
+        <v>329</v>
+      </c>
+      <c r="B501" s="0">
+        <v>6.7461823228288482</v>
+      </c>
+      <c r="C501" s="0">
+        <v>4.1086908460002611</v>
+      </c>
+      <c r="D501" s="0">
+        <v>-2.5234441272409036</v>
+      </c>
+      <c r="E501" s="0">
+        <v>2</v>
+      </c>
+      <c r="F501" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="0" t="s">
+        <v>263</v>
+      </c>
+      <c r="B502" s="0">
+        <v>8.7448348107637699</v>
+      </c>
+      <c r="C502" s="0">
+        <v>4.3199285646971282</v>
+      </c>
+      <c r="D502" s="0">
+        <v>-5.3251174030146435</v>
+      </c>
+      <c r="E502" s="0">
+        <v>2</v>
+      </c>
+      <c r="F502" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="B503" s="0">
+        <v>6.6023908514243841</v>
+      </c>
+      <c r="C503" s="0">
+        <v>1.0152602658884378</v>
+      </c>
+      <c r="D503" s="0">
+        <v>-4.4050770684156761</v>
+      </c>
+      <c r="E503" s="0">
+        <v>2</v>
+      </c>
+      <c r="F503" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="B504" s="0">
+        <v>5.735827108119147</v>
+      </c>
+      <c r="C504" s="0">
+        <v>2.4295812835801227</v>
+      </c>
+      <c r="D504" s="0">
+        <v>-1.971599896794038</v>
+      </c>
+      <c r="E504" s="0">
+        <v>2</v>
+      </c>
+      <c r="F504" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="B505" s="0">
+        <v>4.6344638527112885</v>
+      </c>
+      <c r="C505" s="0">
+        <v>2.0748952953292434</v>
+      </c>
+      <c r="D505" s="0">
+        <v>2.0490841179394419</v>
+      </c>
+      <c r="E505" s="0">
+        <v>2</v>
+      </c>
+      <c r="F505" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="0" t="s">
+        <v>330</v>
+      </c>
+      <c r="B506" s="0">
+        <v>2.9779007335011722</v>
+      </c>
+      <c r="C506" s="0">
+        <v>1.1864795931393688</v>
+      </c>
+      <c r="D506" s="0">
+        <v>1.8529430841020722</v>
+      </c>
+      <c r="E506" s="0">
+        <v>2</v>
+      </c>
+      <c r="F506" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="0" t="s">
+        <v>331</v>
+      </c>
+      <c r="B507" s="0">
+        <v>4.6343452371192981</v>
+      </c>
+      <c r="C507" s="0">
+        <v>1.2969615167605635</v>
+      </c>
+      <c r="D507" s="0">
+        <v>0.63119233403167063</v>
+      </c>
+      <c r="E507" s="0">
+        <v>2</v>
+      </c>
+      <c r="F507" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="0" t="s">
+        <v>332</v>
+      </c>
+      <c r="B508" s="0">
+        <v>-2.0199003426051743</v>
+      </c>
+      <c r="C508" s="0">
+        <v>-2.4758587232161293</v>
+      </c>
+      <c r="D508" s="0">
+        <v>1.5559864003782293</v>
+      </c>
+      <c r="E508" s="0">
+        <v>2</v>
+      </c>
+      <c r="F508" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="B509" s="0">
+        <v>4.42054517964322</v>
+      </c>
+      <c r="C509" s="0">
+        <v>2.3010116836435128</v>
+      </c>
+      <c r="D509" s="0">
+        <v>-1.8696298818558466</v>
+      </c>
+      <c r="E509" s="0">
+        <v>2</v>
+      </c>
+      <c r="F509" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="B510" s="0">
+        <v>9.3209570702510067</v>
+      </c>
+      <c r="C510" s="0">
+        <v>2.0156479512388898</v>
+      </c>
+      <c r="D510" s="0">
+        <v>-2.0948417473467553</v>
+      </c>
+      <c r="E510" s="0">
+        <v>2</v>
+      </c>
+      <c r="F510" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="0" t="s">
+        <v>333</v>
+      </c>
+      <c r="B511" s="0">
+        <v>2.7456027878631808</v>
+      </c>
+      <c r="C511" s="0">
+        <v>1.3402601760821142</v>
+      </c>
+      <c r="D511" s="0">
+        <v>-0.85630976293984395</v>
+      </c>
+      <c r="E511" s="0">
+        <v>2</v>
+      </c>
+      <c r="F511" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="0" t="s">
+        <v>333</v>
+      </c>
+      <c r="B512" s="0">
+        <v>2.7456027878631808</v>
+      </c>
+      <c r="C512" s="0">
+        <v>1.3402601760821142</v>
+      </c>
+      <c r="D512" s="0">
+        <v>-0.85630976293984395</v>
+      </c>
+      <c r="E512" s="0">
+        <v>2</v>
+      </c>
+      <c r="F512" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="0" t="s">
+        <v>334</v>
+      </c>
+      <c r="B513" s="0">
+        <v>9.5442839399782944</v>
+      </c>
+      <c r="C513" s="0">
+        <v>0.88833509888553397</v>
+      </c>
+      <c r="D513" s="0">
+        <v>-0.99007673037242605</v>
+      </c>
+      <c r="E513" s="0">
+        <v>2</v>
+      </c>
+      <c r="F513" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="0" t="s">
+        <v>222</v>
+      </c>
+      <c r="B514" s="0">
+        <v>16.104375562769448</v>
+      </c>
+      <c r="C514" s="0">
+        <v>7.1821946783751889</v>
+      </c>
+      <c r="D514" s="0">
+        <v>-0.92979852011837238</v>
+      </c>
+      <c r="E514" s="0">
+        <v>2</v>
+      </c>
+      <c r="F514" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="0" t="s">
+        <v>223</v>
+      </c>
+      <c r="B515" s="0">
+        <v>9.9228073178730529</v>
+      </c>
+      <c r="C515" s="0">
+        <v>3.7832296519525777</v>
+      </c>
+      <c r="D515" s="0">
+        <v>-0.10967007210637399</v>
+      </c>
+      <c r="E515" s="0">
+        <v>2</v>
+      </c>
+      <c r="F515" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="0" t="s">
+        <v>227</v>
+      </c>
+      <c r="B516" s="0">
+        <v>2.3731319435785636</v>
+      </c>
+      <c r="C516" s="0">
+        <v>0.51820603148448696</v>
+      </c>
+      <c r="D516" s="0">
+        <v>-0.80813809184421037</v>
+      </c>
+      <c r="E516" s="0">
+        <v>2</v>
+      </c>
+      <c r="F516" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="B517" s="0">
+        <v>4.8156224328820487</v>
+      </c>
+      <c r="C517" s="0">
+        <v>1.8731338567082259</v>
+      </c>
+      <c r="D517" s="0">
+        <v>-1.6645887852105603</v>
+      </c>
+      <c r="E517" s="0">
+        <v>2</v>
+      </c>
+      <c r="F517" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="B518" s="0">
+        <v>3.5724561209901862</v>
+      </c>
+      <c r="C518" s="0">
+        <v>3.0191148301834776</v>
+      </c>
+      <c r="D518" s="0">
+        <v>21.700582503413482</v>
+      </c>
+      <c r="E518" s="0">
+        <v>2</v>
+      </c>
+      <c r="F518" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="B519" s="0">
+        <v>3.5724561209901862</v>
+      </c>
+      <c r="C519" s="0">
+        <v>3.0191148301834776</v>
+      </c>
+      <c r="D519" s="0">
+        <v>21.700582503413482</v>
+      </c>
+      <c r="E519" s="0">
+        <v>2</v>
+      </c>
+      <c r="F519" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="0" t="s">
+        <v>227</v>
+      </c>
+      <c r="B520" s="0">
+        <v>2.3731319435785636</v>
+      </c>
+      <c r="C520" s="0">
+        <v>0.51820603148448696</v>
+      </c>
+      <c r="D520" s="0">
+        <v>-0.80813809184421037</v>
+      </c>
+      <c r="E520" s="0">
+        <v>2</v>
+      </c>
+      <c r="F520" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="0" t="s">
+        <v>335</v>
+      </c>
+      <c r="B521" s="0">
+        <v>3.9781763899086875</v>
+      </c>
+      <c r="C521" s="0">
+        <v>4.329341925980053</v>
+      </c>
+      <c r="D521" s="0">
+        <v>-58.583035893953827</v>
+      </c>
+      <c r="E521" s="0">
+        <v>3</v>
+      </c>
+      <c r="F521" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="0" t="s">
+        <v>336</v>
+      </c>
+      <c r="B522" s="0">
+        <v>1.2636078671989799</v>
+      </c>
+      <c r="C522" s="0">
+        <v>0.83855874448379586</v>
+      </c>
+      <c r="D522" s="0">
+        <v>-68.470418649128703</v>
+      </c>
+      <c r="E522" s="0">
+        <v>3</v>
+      </c>
+      <c r="F522" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="0" t="s">
+        <v>337</v>
+      </c>
+      <c r="B523" s="0">
+        <v>1.5866628036077073</v>
+      </c>
+      <c r="C523" s="0">
+        <v>0.80215627426725267</v>
+      </c>
+      <c r="D523" s="0">
+        <v>-113.82135263980165</v>
+      </c>
+      <c r="E523" s="0">
+        <v>3</v>
+      </c>
+      <c r="F523" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B524" s="0">
+        <v>1.4775260062629401</v>
+      </c>
+      <c r="C524" s="0">
+        <v>1.1019534998599427</v>
+      </c>
+      <c r="D524" s="0">
+        <v>-92.278626736144858</v>
+      </c>
+      <c r="E524" s="0">
+        <v>3</v>
+      </c>
+      <c r="F524" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="B525" s="0">
+        <v>1.4410268778369191</v>
+      </c>
+      <c r="C525" s="0">
+        <v>0.067039301315884134</v>
+      </c>
+      <c r="D525" s="0">
+        <v>-49.269538696188548</v>
+      </c>
+      <c r="E525" s="0">
+        <v>3</v>
+      </c>
+      <c r="F525" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B526" s="0">
+        <v>7.7758419564392982</v>
+      </c>
+      <c r="C526" s="0">
+        <v>2.0325512193642323</v>
+      </c>
+      <c r="D526" s="0">
+        <v>-67.880557029372284</v>
+      </c>
+      <c r="E526" s="0">
+        <v>3</v>
+      </c>
+      <c r="F526" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="0" t="s">
+        <v>335</v>
+      </c>
+      <c r="B527" s="0">
+        <v>3.9781763899086875</v>
+      </c>
+      <c r="C527" s="0">
+        <v>4.329341925980053</v>
+      </c>
+      <c r="D527" s="0">
+        <v>-58.583035893953827</v>
+      </c>
+      <c r="E527" s="0">
+        <v>3</v>
+      </c>
+      <c r="F527" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B528" s="0">
+        <v>4.8282139870310283</v>
+      </c>
+      <c r="C528" s="0">
+        <v>3.2375568393508085</v>
+      </c>
+      <c r="D528" s="0">
+        <v>-74.188694518908534</v>
+      </c>
+      <c r="E528" s="0">
+        <v>3</v>
+      </c>
+      <c r="F528" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="B529" s="0">
+        <v>18.53759669561131</v>
+      </c>
+      <c r="C529" s="0">
+        <v>11.639835721866971</v>
+      </c>
+      <c r="D529" s="0">
+        <v>-87.514109981084033</v>
+      </c>
+      <c r="E529" s="0">
+        <v>3</v>
+      </c>
+      <c r="F529" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B530" s="0">
+        <v>10.34094448785334</v>
+      </c>
+      <c r="C530" s="0">
+        <v>1.4670630170044621</v>
+      </c>
+      <c r="D530" s="0">
+        <v>-60.665801432959249</v>
+      </c>
+      <c r="E530" s="0">
+        <v>3</v>
+      </c>
+      <c r="F530" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B531" s="0">
+        <v>0.56998611566115187</v>
+      </c>
+      <c r="C531" s="0">
+        <v>0.11785186587757307</v>
+      </c>
+      <c r="D531" s="0">
+        <v>-81.319114218728714</v>
+      </c>
+      <c r="E531" s="0">
+        <v>3</v>
+      </c>
+      <c r="F531" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="0" t="s">
+        <v>338</v>
+      </c>
+      <c r="B532" s="0">
+        <v>0.42150847424406757</v>
+      </c>
+      <c r="C532" s="0">
+        <v>-0.50404458844720967</v>
+      </c>
+      <c r="D532" s="0">
+        <v>-84.468945489016448</v>
+      </c>
+      <c r="E532" s="0">
+        <v>3</v>
+      </c>
+      <c r="F532" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="0" t="s">
+        <v>339</v>
+      </c>
+      <c r="B533" s="0">
+        <v>1.3238059940842106</v>
+      </c>
+      <c r="C533" s="0">
+        <v>0.33330639975020027</v>
+      </c>
+      <c r="D533" s="0">
+        <v>-116.10078541274812</v>
+      </c>
+      <c r="E533" s="0">
+        <v>3</v>
+      </c>
+      <c r="F533" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="0" t="s">
+        <v>340</v>
+      </c>
+      <c r="B534" s="0">
+        <v>0.4693058645058773</v>
+      </c>
+      <c r="C534" s="0">
+        <v>-0.084467465776790387</v>
+      </c>
+      <c r="D534" s="0">
+        <v>-76.859219092620847</v>
+      </c>
+      <c r="E534" s="0">
+        <v>3</v>
+      </c>
+      <c r="F534" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="0" t="s">
+        <v>341</v>
+      </c>
+      <c r="B535" s="0">
+        <v>-1.9080386721931686</v>
+      </c>
+      <c r="C535" s="0">
+        <v>-2.0907709927070832</v>
+      </c>
+      <c r="D535" s="0">
+        <v>-116.91047571268061</v>
+      </c>
+      <c r="E535" s="0">
+        <v>3</v>
+      </c>
+      <c r="F535" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="0" t="s">
+        <v>342</v>
+      </c>
+      <c r="B536" s="0">
+        <v>0.23823441270928641</v>
+      </c>
+      <c r="C536" s="0">
+        <v>-0.54476494398506548</v>
+      </c>
+      <c r="D536" s="0">
+        <v>-115.83666942915936</v>
+      </c>
+      <c r="E536" s="0">
+        <v>3</v>
+      </c>
+      <c r="F536" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="0" t="s">
+        <v>343</v>
+      </c>
+      <c r="B537" s="0">
+        <v>0.15249605572566949</v>
+      </c>
+      <c r="C537" s="0">
+        <v>-0.13684093090226976</v>
+      </c>
+      <c r="D537" s="0">
+        <v>-116.70191570646267</v>
+      </c>
+      <c r="E537" s="0">
+        <v>3</v>
+      </c>
+      <c r="F537" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="B538" s="0">
+        <v>0.42786966855623909</v>
+      </c>
+      <c r="C538" s="0">
+        <v>0.010398742844543904</v>
+      </c>
+      <c r="D538" s="0">
+        <v>-116.11053376340833</v>
+      </c>
+      <c r="E538" s="0">
+        <v>3</v>
+      </c>
+      <c r="F538" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="0" t="s">
+        <v>342</v>
+      </c>
+      <c r="B539" s="0">
+        <v>0.23823441270928641</v>
+      </c>
+      <c r="C539" s="0">
+        <v>-0.54476494398506548</v>
+      </c>
+      <c r="D539" s="0">
+        <v>-115.83666942915936</v>
+      </c>
+      <c r="E539" s="0">
+        <v>3</v>
+      </c>
+      <c r="F539" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="0" t="s">
+        <v>233</v>
+      </c>
+      <c r="B540" s="0">
+        <v>4.8917332307477235</v>
+      </c>
+      <c r="C540" s="0">
+        <v>3.9954698006354681</v>
+      </c>
+      <c r="D540" s="0">
+        <v>-68.753012446769588</v>
+      </c>
+      <c r="E540" s="0">
+        <v>3</v>
+      </c>
+      <c r="F540" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="0" t="s">
+        <v>344</v>
+      </c>
+      <c r="B541" s="0">
+        <v>0.23110651013189812</v>
+      </c>
+      <c r="C541" s="0">
+        <v>-0.20864025302117944</v>
+      </c>
+      <c r="D541" s="0">
+        <v>-118.64791201713557</v>
+      </c>
+      <c r="E541" s="0">
+        <v>3</v>
+      </c>
+      <c r="F541" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="0" t="s">
+        <v>345</v>
+      </c>
+      <c r="B542" s="0">
+        <v>5.9350824912999292</v>
+      </c>
+      <c r="C542" s="0">
+        <v>3.2028598231557179</v>
+      </c>
+      <c r="D542" s="0">
+        <v>-57.985998456367</v>
+      </c>
+      <c r="E542" s="0">
+        <v>3</v>
+      </c>
+      <c r="F542" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="0" t="s">
+        <v>346</v>
+      </c>
+      <c r="B543" s="0">
+        <v>1.4543618186822633</v>
+      </c>
+      <c r="C543" s="0">
+        <v>2.2159604544116727</v>
+      </c>
+      <c r="D543" s="0">
+        <v>-65.154815292568784</v>
+      </c>
+      <c r="E543" s="0">
+        <v>3</v>
+      </c>
+      <c r="F543" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="0" t="s">
+        <v>344</v>
+      </c>
+      <c r="B544" s="0">
+        <v>0.23110651013189812</v>
+      </c>
+      <c r="C544" s="0">
+        <v>-0.20864025302117944</v>
+      </c>
+      <c r="D544" s="0">
+        <v>-118.64791201713557</v>
+      </c>
+      <c r="E544" s="0">
+        <v>3</v>
+      </c>
+      <c r="F544" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="0" t="s">
+        <v>347</v>
+      </c>
+      <c r="B545" s="0">
+        <v>3.5658826219969244</v>
+      </c>
+      <c r="C545" s="0">
+        <v>1.1080499938316142</v>
+      </c>
+      <c r="D545" s="0">
+        <v>-62.424554550041385</v>
+      </c>
+      <c r="E545" s="0">
+        <v>3</v>
+      </c>
+      <c r="F545" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="0" t="s">
+        <v>346</v>
+      </c>
+      <c r="B546" s="0">
+        <v>1.4543618186822633</v>
+      </c>
+      <c r="C546" s="0">
+        <v>2.2159604544116727</v>
+      </c>
+      <c r="D546" s="0">
+        <v>-65.154815292568784</v>
+      </c>
+      <c r="E546" s="0">
+        <v>3</v>
+      </c>
+      <c r="F546" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="B547" s="0">
+        <v>3.2319177358033242</v>
+      </c>
+      <c r="C547" s="0">
+        <v>1.4478767465085476</v>
+      </c>
+      <c r="D547" s="0">
+        <v>-115.9404461948548</v>
+      </c>
+      <c r="E547" s="0">
+        <v>3</v>
+      </c>
+      <c r="F547" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="0" t="s">
+        <v>348</v>
+      </c>
+      <c r="B548" s="0">
+        <v>2.1123951452922047</v>
+      </c>
+      <c r="C548" s="0">
+        <v>1.6518582067136915</v>
+      </c>
+      <c r="D548" s="0">
+        <v>-60.458236458152079</v>
+      </c>
+      <c r="E548" s="0">
+        <v>3</v>
+      </c>
+      <c r="F548" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="0" t="s">
+        <v>349</v>
+      </c>
+      <c r="B549" s="0">
+        <v>1.5203787002628648</v>
+      </c>
+      <c r="C549" s="0">
+        <v>0.92214218601198827</v>
+      </c>
+      <c r="D549" s="0">
+        <v>-113.28714499525746</v>
+      </c>
+      <c r="E549" s="0">
+        <v>3</v>
+      </c>
+      <c r="F549" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="0" t="s">
+        <v>350</v>
+      </c>
+      <c r="B550" s="0">
+        <v>2.3531960780111434</v>
+      </c>
+      <c r="C550" s="0">
+        <v>1.7669807018305919</v>
+      </c>
+      <c r="D550" s="0">
+        <v>-63.28583571184366</v>
+      </c>
+      <c r="E550" s="0">
+        <v>3</v>
+      </c>
+      <c r="F550" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="B551" s="0">
+        <v>3.2319177358033242</v>
+      </c>
+      <c r="C551" s="0">
+        <v>1.4478767465085476</v>
+      </c>
+      <c r="D551" s="0">
+        <v>-115.9404461948548</v>
+      </c>
+      <c r="E551" s="0">
+        <v>3</v>
+      </c>
+      <c r="F551" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="0" t="s">
+        <v>351</v>
+      </c>
+      <c r="B552" s="0">
+        <v>3.3464183302546529</v>
+      </c>
+      <c r="C552" s="0">
+        <v>3.0973755484761147</v>
+      </c>
+      <c r="D552" s="0">
+        <v>-53.849960759844606</v>
+      </c>
+      <c r="E552" s="0">
+        <v>3</v>
+      </c>
+      <c r="F552" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B553" s="0">
+        <v>0.046018204071921955</v>
+      </c>
+      <c r="C553" s="0">
+        <v>-1.0300836820809838</v>
+      </c>
+      <c r="D553" s="0">
+        <v>-52.650232805483498</v>
+      </c>
+      <c r="E553" s="0">
+        <v>3</v>
+      </c>
+      <c r="F553" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="0" t="s">
+        <v>352</v>
+      </c>
+      <c r="B554" s="0">
+        <v>-0.70077152299304113</v>
+      </c>
+      <c r="C554" s="0">
+        <v>2.446926074605662</v>
+      </c>
+      <c r="D554" s="0">
+        <v>-49.33618569817196</v>
+      </c>
+      <c r="E554" s="0">
+        <v>3</v>
+      </c>
+      <c r="F554" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B555" s="0">
+        <v>0.4738463070423069</v>
+      </c>
+      <c r="C555" s="0">
+        <v>-8.8439803879705821</v>
+      </c>
+      <c r="D555" s="0">
+        <v>-45.549017946753239</v>
+      </c>
+      <c r="E555" s="0">
+        <v>3</v>
+      </c>
+      <c r="F555" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="0" t="s">
+        <v>353</v>
+      </c>
+      <c r="B556" s="0">
+        <v>1.7828641826751042</v>
+      </c>
+      <c r="C556" s="0">
+        <v>1.9243001842203198</v>
+      </c>
+      <c r="D556" s="0">
+        <v>-71.333613872361724</v>
+      </c>
+      <c r="E556" s="0">
+        <v>3</v>
+      </c>
+      <c r="F556" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B557" s="0">
+        <v>0.28536519504182056</v>
+      </c>
+      <c r="C557" s="0">
+        <v>1.8430470226741289</v>
+      </c>
+      <c r="D557" s="0">
+        <v>-52.584176397112529</v>
+      </c>
+      <c r="E557" s="0">
+        <v>3</v>
+      </c>
+      <c r="F557" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B558" s="0">
+        <v>-2.1985705349383773</v>
+      </c>
+      <c r="C558" s="0">
+        <v>-0.45095837778008185</v>
+      </c>
+      <c r="D558" s="0">
+        <v>-61.710587362195142</v>
+      </c>
+      <c r="E558" s="0">
+        <v>3</v>
+      </c>
+      <c r="F558" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="0" t="s">
+        <v>354</v>
+      </c>
+      <c r="B559" s="0">
+        <v>0.69343033964438827</v>
+      </c>
+      <c r="C559" s="0">
+        <v>-0.13828869617097875</v>
+      </c>
+      <c r="D559" s="0">
+        <v>-116.8649233074827</v>
+      </c>
+      <c r="E559" s="0">
+        <v>3</v>
+      </c>
+      <c r="F559" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="0" t="s">
+        <v>355</v>
+      </c>
+      <c r="B560" s="0">
+        <v>1.2032177119095218</v>
+      </c>
+      <c r="C560" s="0">
+        <v>0.98874437605857624</v>
+      </c>
+      <c r="D560" s="0">
+        <v>-120.19195772957936</v>
+      </c>
+      <c r="E560" s="0">
+        <v>3</v>
+      </c>
+      <c r="F560" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="B561" s="0">
+        <v>-0.54604526820045429</v>
+      </c>
+      <c r="C561" s="0">
+        <v>-0.89728477661719952</v>
+      </c>
+      <c r="D561" s="0">
+        <v>-65.198924403279165</v>
+      </c>
+      <c r="E561" s="0">
+        <v>3</v>
+      </c>
+      <c r="F561" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="0" t="s">
+        <v>357</v>
+      </c>
+      <c r="B562" s="0">
+        <v>0.98043581352121267</v>
+      </c>
+      <c r="C562" s="0">
+        <v>0.36095543544881714</v>
+      </c>
+      <c r="D562" s="0">
+        <v>-65.085731390446313</v>
+      </c>
+      <c r="E562" s="0">
+        <v>3</v>
+      </c>
+      <c r="F562" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="0" t="s">
+        <v>358</v>
+      </c>
+      <c r="B563" s="0">
+        <v>1.3745009250464311</v>
+      </c>
+      <c r="C563" s="0">
+        <v>0.66182527317337103</v>
+      </c>
+      <c r="D563" s="0">
+        <v>-71.321825734405834</v>
+      </c>
+      <c r="E563" s="0">
+        <v>3</v>
+      </c>
+      <c r="F563" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="0" t="s">
+        <v>354</v>
+      </c>
+      <c r="B564" s="0">
+        <v>0.69343033964438827</v>
+      </c>
+      <c r="C564" s="0">
+        <v>-0.13828869617097875</v>
+      </c>
+      <c r="D564" s="0">
+        <v>-116.8649233074827</v>
+      </c>
+      <c r="E564" s="0">
+        <v>3</v>
+      </c>
+      <c r="F564" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B565" s="0">
+        <v>-1.5758670980001157</v>
+      </c>
+      <c r="C565" s="0">
+        <v>-0.78142137207629536</v>
+      </c>
+      <c r="D565" s="0">
+        <v>-52.946014835699373</v>
+      </c>
+      <c r="E565" s="0">
+        <v>3</v>
+      </c>
+      <c r="F565" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="0" t="s">
+        <v>359</v>
+      </c>
+      <c r="B566" s="0">
+        <v>2.2228771863316932</v>
+      </c>
+      <c r="C566" s="0">
+        <v>1.6260211348641589</v>
+      </c>
+      <c r="D566" s="0">
+        <v>-67.642781259815507</v>
+      </c>
+      <c r="E566" s="0">
+        <v>3</v>
+      </c>
+      <c r="F566" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="B567" s="0">
+        <v>1.8804103885215895</v>
+      </c>
+      <c r="C567" s="0">
+        <v>0.052954696544812538</v>
+      </c>
+      <c r="D567" s="0">
+        <v>-80.168321271467207</v>
+      </c>
+      <c r="E567" s="0">
+        <v>3</v>
+      </c>
+      <c r="F567" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B568" s="0">
+        <v>0.71942667610226141</v>
+      </c>
+      <c r="C568" s="0">
+        <v>-1.7199814847228829</v>
+      </c>
+      <c r="D568" s="0">
+        <v>-74.857627172764211</v>
+      </c>
+      <c r="E568" s="0">
+        <v>3</v>
+      </c>
+      <c r="F568" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B569" s="0">
+        <v>2.2632120354319643</v>
+      </c>
+      <c r="C569" s="0">
+        <v>0.1994809485322962</v>
+      </c>
+      <c r="D569" s="0">
+        <v>-67.179563602119615</v>
+      </c>
+      <c r="E569" s="0">
+        <v>3</v>
+      </c>
+      <c r="F569" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="B570" s="0">
+        <v>-0.24430867921579774</v>
+      </c>
+      <c r="C570" s="0">
+        <v>0.35964179612300745</v>
+      </c>
+      <c r="D570" s="0">
+        <v>-92.731129344830762</v>
+      </c>
+      <c r="E570" s="0">
+        <v>3</v>
+      </c>
+      <c r="F570" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="B571" s="0">
+        <v>-1.1256529934279331</v>
+      </c>
+      <c r="C571" s="0">
+        <v>-0.044511259172345413</v>
+      </c>
+      <c r="D571" s="0">
+        <v>-122.11031328990779</v>
+      </c>
+      <c r="E571" s="0">
+        <v>3</v>
+      </c>
+      <c r="F571" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="B572" s="0">
+        <v>153.56275576020769</v>
+      </c>
+      <c r="C572" s="0">
+        <v>42.251616945861436</v>
+      </c>
+      <c r="D572" s="0">
+        <v>-3.6751629604320626</v>
+      </c>
+      <c r="E572" s="0">
+        <v>4</v>
+      </c>
+      <c r="F572" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="B573" s="0">
+        <v>154.45333829016425</v>
+      </c>
+      <c r="C573" s="0">
+        <v>40.781823794277493</v>
+      </c>
+      <c r="D573" s="0">
+        <v>-2.0517843098763509</v>
+      </c>
+      <c r="E573" s="0">
+        <v>4</v>
+      </c>
+      <c r="F573" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="B574" s="0">
+        <v>154.45333829016425</v>
+      </c>
+      <c r="C574" s="0">
+        <v>40.781823794277493</v>
+      </c>
+      <c r="D574" s="0">
+        <v>-2.0517843098763509</v>
+      </c>
+      <c r="E574" s="0">
+        <v>4</v>
+      </c>
+      <c r="F574" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="0" t="s">
+        <v>329</v>
+      </c>
+      <c r="B575" s="0">
+        <v>152.01375220816837</v>
+      </c>
+      <c r="C575" s="0">
+        <v>38.712685733918924</v>
+      </c>
+      <c r="D575" s="0">
+        <v>1.2865445247689868</v>
+      </c>
+      <c r="E575" s="0">
+        <v>4</v>
+      </c>
+      <c r="F575" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="0" t="s">
+        <v>360</v>
+      </c>
+      <c r="B576" s="0">
+        <v>153.688396951968</v>
+      </c>
+      <c r="C576" s="0">
+        <v>53.920616475356418</v>
+      </c>
+      <c r="D576" s="0">
+        <v>-1.096675665903958</v>
+      </c>
+      <c r="E576" s="0">
+        <v>4</v>
+      </c>
+      <c r="F576" s="0" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="0" t="s">
+        <v>361</v>
+      </c>
+      <c r="B577" s="0">
+        <v>165.7907295696838</v>
+      </c>
+      <c r="C577" s="0">
+        <v>92.308621255185415</v>
+      </c>
+      <c r="D577" s="0">
+        <v>-37.223627565453796</v>
+      </c>
+      <c r="E577" s="0">
+        <v>4</v>
+      </c>
+      <c r="F577" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="0" t="s">
+        <v>175</v>
+      </c>
+      <c r="B578" s="0">
+        <v>154.28001126008186</v>
+      </c>
+      <c r="C578" s="0">
+        <v>46.938833941012106</v>
+      </c>
+      <c r="D578" s="0">
+        <v>-21.59663839460886</v>
+      </c>
+      <c r="E578" s="0">
+        <v>4</v>
+      </c>
+      <c r="F578" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="0" t="s">
+        <v>175</v>
+      </c>
+      <c r="B579" s="0">
+        <v>154.28001126008186</v>
+      </c>
+      <c r="C579" s="0">
+        <v>46.938833941012106</v>
+      </c>
+      <c r="D579" s="0">
+        <v>-21.59663839460886</v>
+      </c>
+      <c r="E579" s="0">
+        <v>4</v>
+      </c>
+      <c r="F579" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="0" t="s">
+        <v>363</v>
+      </c>
+      <c r="B580" s="0">
+        <v>-0.41671378471629084</v>
+      </c>
+      <c r="C580" s="0">
+        <v>-4.32396247249007</v>
+      </c>
+      <c r="D580" s="0">
+        <v>-7.1788674357405613</v>
+      </c>
+      <c r="E580" s="0">
+        <v>5</v>
+      </c>
+      <c r="F580" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="0" t="s">
+        <v>318</v>
+      </c>
+      <c r="B581" s="0">
+        <v>2.5684200246390607</v>
+      </c>
+      <c r="C581" s="0">
+        <v>1.0031402732433325</v>
+      </c>
+      <c r="D581" s="0">
+        <v>-3.7749515387976902</v>
+      </c>
+      <c r="E581" s="0">
+        <v>5</v>
+      </c>
+      <c r="F581" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="0" t="s">
+        <v>364</v>
+      </c>
+      <c r="B582" s="0">
+        <v>3.5461982964200649</v>
+      </c>
+      <c r="C582" s="0">
+        <v>0.24561146612305482</v>
+      </c>
+      <c r="D582" s="0">
+        <v>-5.7807602480584608</v>
+      </c>
+      <c r="E582" s="0">
+        <v>5</v>
+      </c>
+      <c r="F582" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="B583" s="0">
+        <v>5.9828135980281232</v>
+      </c>
+      <c r="C583" s="0">
+        <v>2.1007065850845468</v>
+      </c>
+      <c r="D583" s="0">
+        <v>-10.248482671842895</v>
+      </c>
+      <c r="E583" s="0">
+        <v>5</v>
+      </c>
+      <c r="F583" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="0" t="s">
+        <v>365</v>
+      </c>
+      <c r="B584" s="0">
+        <v>1.2991913872422423</v>
+      </c>
+      <c r="C584" s="0">
+        <v>-0.67872281770178999</v>
+      </c>
+      <c r="D584" s="0">
+        <v>-1.2299076576309587</v>
+      </c>
+      <c r="E584" s="0">
+        <v>5</v>
+      </c>
+      <c r="F584" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="0" t="s">
+        <v>366</v>
+      </c>
+      <c r="B585" s="0">
+        <v>3.5895597949034213</v>
+      </c>
+      <c r="C585" s="0">
+        <v>0.3009876402600653</v>
+      </c>
+      <c r="D585" s="0">
+        <v>-2.8767819606067846</v>
+      </c>
+      <c r="E585" s="0">
+        <v>5</v>
+      </c>
+      <c r="F585" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="0" t="s">
+        <v>367</v>
+      </c>
+      <c r="B586" s="0">
+        <v>3.849615382606201</v>
+      </c>
+      <c r="C586" s="0">
+        <v>1.035149817833712</v>
+      </c>
+      <c r="D586" s="0">
+        <v>-4.6758938947806463</v>
+      </c>
+      <c r="E586" s="0">
+        <v>5</v>
+      </c>
+      <c r="F586" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="B587" s="0">
+        <v>1.4551103118661326</v>
+      </c>
+      <c r="C587" s="0">
+        <v>-0.35400139217683008</v>
+      </c>
+      <c r="D587" s="0">
+        <v>-1.434320514261388</v>
+      </c>
+      <c r="E587" s="0">
+        <v>5</v>
+      </c>
+      <c r="F587" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="B588" s="0">
+        <v>7.1817231323198243</v>
+      </c>
+      <c r="C588" s="0">
+        <v>3.9098506562243118</v>
+      </c>
+      <c r="D588" s="0">
+        <v>-7.6318291322209193</v>
+      </c>
+      <c r="E588" s="0">
+        <v>5</v>
+      </c>
+      <c r="F588" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="B589" s="0">
+        <v>0.97357671628633036</v>
+      </c>
+      <c r="C589" s="0">
+        <v>-3.4155608372727748</v>
+      </c>
+      <c r="D589" s="0">
+        <v>-4.6728675604247201</v>
+      </c>
+      <c r="E589" s="0">
+        <v>5</v>
+      </c>
+      <c r="F589" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="0" t="s">
+        <v>368</v>
+      </c>
+      <c r="B590" s="0">
+        <v>0.79095951245432683</v>
+      </c>
+      <c r="C590" s="0">
+        <v>-8.1545855581899627</v>
+      </c>
+      <c r="D590" s="0">
+        <v>-1.1741696173766847</v>
+      </c>
+      <c r="E590" s="0">
+        <v>5</v>
+      </c>
+      <c r="F590" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="B591" s="0">
+        <v>4.8417303027551188</v>
+      </c>
+      <c r="C591" s="0">
+        <v>2.314192212837336</v>
+      </c>
+      <c r="D591" s="0">
+        <v>-10.909711211434123</v>
+      </c>
+      <c r="E591" s="0">
+        <v>5</v>
+      </c>
+      <c r="F591" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="B592" s="0">
+        <v>3.0645427156731238</v>
+      </c>
+      <c r="C592" s="0">
+        <v>1.4339331884062763</v>
+      </c>
+      <c r="D592" s="0">
+        <v>-2.8876737278303599</v>
+      </c>
+      <c r="E592" s="0">
+        <v>5</v>
+      </c>
+      <c r="F592" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="B593" s="0">
+        <v>3.9203443076590774</v>
+      </c>
+      <c r="C593" s="0">
+        <v>-1.4477722187174311</v>
+      </c>
+      <c r="D593" s="0">
+        <v>-3.1895106528180905</v>
+      </c>
+      <c r="E593" s="0">
+        <v>5</v>
+      </c>
+      <c r="F593" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="B594" s="0">
+        <v>2.2767525211377135</v>
+      </c>
+      <c r="C594" s="0">
+        <v>-2.1742107106900526</v>
+      </c>
+      <c r="D594" s="0">
+        <v>-3.436886431727419</v>
+      </c>
+      <c r="E594" s="0">
+        <v>5</v>
+      </c>
+      <c r="F594" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="0" t="s">
+        <v>369</v>
+      </c>
+      <c r="B595" s="0">
+        <v>1.0766213402864333</v>
+      </c>
+      <c r="C595" s="0">
+        <v>-1.5624227368197683</v>
+      </c>
+      <c r="D595" s="0">
+        <v>-11.565814619508837</v>
+      </c>
+      <c r="E595" s="0">
+        <v>5</v>
+      </c>
+      <c r="F595" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="B596" s="0">
+        <v>2.6537273183728418</v>
+      </c>
+      <c r="C596" s="0">
+        <v>0.45985610780180691</v>
+      </c>
+      <c r="D596" s="0">
+        <v>-5.7954301847216954</v>
+      </c>
+      <c r="E596" s="0">
+        <v>5</v>
+      </c>
+      <c r="F596" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="B597" s="0">
+        <v>-95.232867486920156</v>
+      </c>
+      <c r="C597" s="0">
+        <v>-97.530633379485607</v>
+      </c>
+      <c r="D597" s="0">
+        <v>0.37324202369688714</v>
+      </c>
+      <c r="E597" s="0">
+        <v>5</v>
+      </c>
+      <c r="F597" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="B598" s="0">
+        <v>3.5463281964558284</v>
+      </c>
+      <c r="C598" s="0">
+        <v>1.38475979021323</v>
+      </c>
+      <c r="D598" s="0">
+        <v>-8.2261320107493905</v>
+      </c>
+      <c r="E598" s="0">
+        <v>5</v>
+      </c>
+      <c r="F598" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="0" t="s">
+        <v>370</v>
+      </c>
+      <c r="B599" s="0">
+        <v>1.4783369742109389</v>
+      </c>
+      <c r="C599" s="0">
+        <v>0.049018541398355403</v>
+      </c>
+      <c r="D599" s="0">
+        <v>-4.2711691072719447</v>
+      </c>
+      <c r="E599" s="0">
+        <v>5</v>
+      </c>
+      <c r="F599" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="B600" s="0">
+        <v>2.8727010870408476</v>
+      </c>
+      <c r="C600" s="0">
+        <v>0.7725108269384412</v>
+      </c>
+      <c r="D600" s="0">
+        <v>-2.9917022715431258</v>
+      </c>
+      <c r="E600" s="0">
+        <v>5</v>
+      </c>
+      <c r="F600" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B601" s="0">
+        <v>2.7040550941106791</v>
+      </c>
+      <c r="C601" s="0">
+        <v>0.78619678950886951</v>
+      </c>
+      <c r="D601" s="0">
+        <v>-7.8494905559389139</v>
+      </c>
+      <c r="E601" s="0">
+        <v>5</v>
+      </c>
+      <c r="F601" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="B602" s="0">
+        <v>6.2382597804167617</v>
+      </c>
+      <c r="C602" s="0">
+        <v>0.89409953428452826</v>
+      </c>
+      <c r="D602" s="0">
+        <v>-6.7341836034494493</v>
+      </c>
+      <c r="E602" s="0">
+        <v>5</v>
+      </c>
+      <c r="F602" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="B603" s="0">
+        <v>3.1769159455518627</v>
+      </c>
+      <c r="C603" s="0">
+        <v>1.7922851122391372</v>
+      </c>
+      <c r="D603" s="0">
+        <v>-3.4389297989386622</v>
+      </c>
+      <c r="E603" s="0">
+        <v>5</v>
+      </c>
+      <c r="F603" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="B604" s="0">
+        <v>1.3833932335580503</v>
+      </c>
+      <c r="C604" s="0">
+        <v>0.21178932606954948</v>
+      </c>
+      <c r="D604" s="0">
+        <v>-2.1988294526322227</v>
+      </c>
+      <c r="E604" s="0">
+        <v>5</v>
+      </c>
+      <c r="F604" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="B605" s="0">
+        <v>2.363663779361687</v>
+      </c>
+      <c r="C605" s="0">
+        <v>-0.41672324221827323</v>
+      </c>
+      <c r="D605" s="0">
+        <v>-3.0479582514332262</v>
+      </c>
+      <c r="E605" s="0">
+        <v>5</v>
+      </c>
+      <c r="F605" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="B606" s="0">
+        <v>0.56763949678119197</v>
+      </c>
+      <c r="C606" s="0">
+        <v>-2.0084942945807125</v>
+      </c>
+      <c r="D606" s="0">
+        <v>-6.6640911062612762</v>
+      </c>
+      <c r="E606" s="0">
+        <v>5</v>
+      </c>
+      <c r="F606" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="B607" s="0">
+        <v>3.4051311775343449</v>
+      </c>
+      <c r="C607" s="0">
+        <v>1.3460400390057956</v>
+      </c>
+      <c r="D607" s="0">
+        <v>-7.9292284800001722</v>
+      </c>
+      <c r="E607" s="0">
+        <v>5</v>
+      </c>
+      <c r="F607" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="B608" s="0">
+        <v>0.81320015433363568</v>
+      </c>
+      <c r="C608" s="0">
+        <v>-0.4686565551478753</v>
+      </c>
+      <c r="D608" s="0">
+        <v>-2.4487514352630178</v>
+      </c>
+      <c r="E608" s="0">
+        <v>5</v>
+      </c>
+      <c r="F608" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="B609" s="0">
+        <v>4.2909274197476579</v>
+      </c>
+      <c r="C609" s="0">
+        <v>0.41884704494897557</v>
+      </c>
+      <c r="D609" s="0">
+        <v>-5.0036959306674351</v>
+      </c>
+      <c r="E609" s="0">
+        <v>5</v>
+      </c>
+      <c r="F609" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="0" t="s">
+        <v>280</v>
+      </c>
+      <c r="B610" s="0">
+        <v>4.4157972938185228</v>
+      </c>
+      <c r="C610" s="0">
+        <v>0.25872073677941321</v>
+      </c>
+      <c r="D610" s="0">
+        <v>-4.2169060784973373</v>
+      </c>
+      <c r="E610" s="0">
+        <v>5</v>
+      </c>
+      <c r="F610" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="B611" s="0">
+        <v>6.2144902675231961</v>
+      </c>
+      <c r="C611" s="0">
+        <v>0.55081852437841883</v>
+      </c>
+      <c r="D611" s="0">
+        <v>-4.5628579715978557</v>
+      </c>
+      <c r="E611" s="0">
+        <v>5</v>
+      </c>
+      <c r="F611" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="B612" s="0">
+        <v>1.1434919222705067</v>
+      </c>
+      <c r="C612" s="0">
+        <v>0.588020527253591</v>
+      </c>
+      <c r="D612" s="0">
+        <v>-9.083546762962154</v>
+      </c>
+      <c r="E612" s="0">
+        <v>5</v>
+      </c>
+      <c r="F612" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="B613" s="0">
+        <v>4.7715754082239163</v>
+      </c>
+      <c r="C613" s="0">
+        <v>-0.40290306257542918</v>
+      </c>
+      <c r="D613" s="0">
+        <v>-7.7936878031865398</v>
+      </c>
+      <c r="E613" s="0">
+        <v>5</v>
+      </c>
+      <c r="F613" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B614" s="0">
+        <v>5.2976221220993098</v>
+      </c>
+      <c r="C614" s="0">
+        <v>0.43223169644888576</v>
+      </c>
+      <c r="D614" s="0">
+        <v>-6.178170931429058</v>
+      </c>
+      <c r="E614" s="0">
+        <v>5</v>
+      </c>
+      <c r="F614" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="0" t="s">
+        <v>371</v>
+      </c>
+      <c r="B615" s="0">
+        <v>2.7692872693001265</v>
+      </c>
+      <c r="C615" s="0">
+        <v>0.30466669999377438</v>
+      </c>
+      <c r="D615" s="0">
+        <v>-2.8367538201309301</v>
+      </c>
+      <c r="E615" s="0">
+        <v>5</v>
+      </c>
+      <c r="F615" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="0" t="s">
+        <v>372</v>
+      </c>
+      <c r="B616" s="0">
+        <v>2.5995735021014297</v>
+      </c>
+      <c r="C616" s="0">
+        <v>0.049418144499619752</v>
+      </c>
+      <c r="D616" s="0">
+        <v>-5.007145952138969</v>
+      </c>
+      <c r="E616" s="0">
+        <v>5</v>
+      </c>
+      <c r="F616" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="0" t="s">
+        <v>313</v>
+      </c>
+      <c r="B617" s="0">
+        <v>4.0838417469936701</v>
+      </c>
+      <c r="C617" s="0">
+        <v>0.70556209730381847</v>
+      </c>
+      <c r="D617" s="0">
+        <v>-4.5580483017694204</v>
+      </c>
+      <c r="E617" s="0">
+        <v>5</v>
+      </c>
+      <c r="F617" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="B618" s="0">
+        <v>1.06410003940631</v>
+      </c>
+      <c r="C618" s="0">
+        <v>-2.6171943420506731</v>
+      </c>
+      <c r="D618" s="0">
+        <v>-4.3833944368160029</v>
+      </c>
+      <c r="E618" s="0">
+        <v>5</v>
+      </c>
+      <c r="F618" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="0" t="s">
+        <v>373</v>
+      </c>
+      <c r="B619" s="0">
+        <v>4.9975823142294518</v>
+      </c>
+      <c r="C619" s="0">
+        <v>0.34011439310502362</v>
+      </c>
+      <c r="D619" s="0">
+        <v>-3.8366451436179925</v>
+      </c>
+      <c r="E619" s="0">
+        <v>5</v>
+      </c>
+      <c r="F619" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="0" t="s">
+        <v>327</v>
+      </c>
+      <c r="B620" s="0">
+        <v>3.2703236358844103</v>
+      </c>
+      <c r="C620" s="0">
+        <v>0.88191390680544512</v>
+      </c>
+      <c r="D620" s="0">
+        <v>-3.0562285696551617</v>
+      </c>
+      <c r="E620" s="0">
+        <v>5</v>
+      </c>
+      <c r="F620" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="0" t="s">
+        <v>374</v>
+      </c>
+      <c r="B621" s="0">
+        <v>2.4428826072351471</v>
+      </c>
+      <c r="C621" s="0">
+        <v>0.32580411850075874</v>
+      </c>
+      <c r="D621" s="0">
+        <v>-4.0662051189146329</v>
+      </c>
+      <c r="E621" s="0">
+        <v>5</v>
+      </c>
+      <c r="F621" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="0" t="s">
+        <v>375</v>
+      </c>
+      <c r="B622" s="0">
+        <v>5.2610993215838455</v>
+      </c>
+      <c r="C622" s="0">
+        <v>2.0780478814566554</v>
+      </c>
+      <c r="D622" s="0">
+        <v>-5.427020740394453</v>
+      </c>
+      <c r="E622" s="0">
+        <v>5</v>
+      </c>
+      <c r="F622" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="0" t="s">
+        <v>310</v>
+      </c>
+      <c r="B623" s="0">
+        <v>1.4667031246316624</v>
+      </c>
+      <c r="C623" s="0">
+        <v>-0.48180943879171401</v>
+      </c>
+      <c r="D623" s="0">
+        <v>-2.791881537175672</v>
+      </c>
+      <c r="E623" s="0">
+        <v>5</v>
+      </c>
+      <c r="F623" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="0" t="s">
+        <v>357</v>
+      </c>
+      <c r="B624" s="0">
+        <v>2.0922033862368501</v>
+      </c>
+      <c r="C624" s="0">
+        <v>1.3015657772003537</v>
+      </c>
+      <c r="D624" s="0">
+        <v>-5.8843223028725884</v>
+      </c>
+      <c r="E624" s="0">
+        <v>5</v>
+      </c>
+      <c r="F624" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="B625" s="0">
+        <v>1.1542614188231859</v>
+      </c>
+      <c r="C625" s="0">
+        <v>-0.088502040425610259</v>
+      </c>
+      <c r="D625" s="0">
+        <v>-1.6918239443133969</v>
+      </c>
+      <c r="E625" s="0">
+        <v>5</v>
+      </c>
+      <c r="F625" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="0" t="s">
+        <v>376</v>
+      </c>
+      <c r="B626" s="0">
+        <v>0.6039048007678407</v>
+      </c>
+      <c r="C626" s="0">
+        <v>-0.53798674734048424</v>
+      </c>
+      <c r="D626" s="0">
+        <v>-4.9043535900335504</v>
+      </c>
+      <c r="E626" s="0">
+        <v>5</v>
+      </c>
+      <c r="F626" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="B627" s="0">
+        <v>2.8727010870408476</v>
+      </c>
+      <c r="C627" s="0">
+        <v>0.7725108269384412</v>
+      </c>
+      <c r="D627" s="0">
+        <v>-2.9917022715431258</v>
+      </c>
+      <c r="E627" s="0">
+        <v>5</v>
+      </c>
+      <c r="F627" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="0" t="s">
+        <v>364</v>
+      </c>
+      <c r="B628" s="0">
+        <v>3.5461982964200649</v>
+      </c>
+      <c r="C628" s="0">
+        <v>0.24561146612305482</v>
+      </c>
+      <c r="D628" s="0">
+        <v>-5.7807602480584608</v>
+      </c>
+      <c r="E628" s="0">
+        <v>5</v>
+      </c>
+      <c r="F628" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="B629" s="0">
+        <v>3.609512342129968</v>
+      </c>
+      <c r="C629" s="0">
+        <v>1.7064465122159878</v>
+      </c>
+      <c r="D629" s="0">
+        <v>-4.1759705617149852</v>
+      </c>
+      <c r="E629" s="0">
+        <v>5</v>
+      </c>
+      <c r="F629" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="B630" s="0">
+        <v>3.2581510190313394</v>
+      </c>
+      <c r="C630" s="0">
+        <v>1.5171564825645936</v>
+      </c>
+      <c r="D630" s="0">
+        <v>-5.2557219300584395</v>
+      </c>
+      <c r="E630" s="0">
+        <v>5</v>
+      </c>
+      <c r="F630" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="B631" s="0">
+        <v>1.3891330714960968</v>
+      </c>
+      <c r="C631" s="0">
+        <v>0.6743841463677176</v>
+      </c>
+      <c r="D631" s="0">
+        <v>-13.062547553920439</v>
+      </c>
+      <c r="E631" s="0">
+        <v>5</v>
+      </c>
+      <c r="F631" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="B632" s="0">
+        <v>2.5797227226753643</v>
+      </c>
+      <c r="C632" s="0">
+        <v>0.72418809659542449</v>
+      </c>
+      <c r="D632" s="0">
+        <v>-5.0022764059174314</v>
+      </c>
+      <c r="E632" s="0">
+        <v>5</v>
+      </c>
+      <c r="F632" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="B633" s="0">
+        <v>3.0645427156731238</v>
+      </c>
+      <c r="C633" s="0">
+        <v>1.4339331884062763</v>
+      </c>
+      <c r="D633" s="0">
+        <v>-2.8876737278303599</v>
+      </c>
+      <c r="E633" s="0">
+        <v>5</v>
+      </c>
+      <c r="F633" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="B634" s="0">
+        <v>3.9203443076590774</v>
+      </c>
+      <c r="C634" s="0">
+        <v>-1.4477722187174311</v>
+      </c>
+      <c r="D634" s="0">
+        <v>-3.1895106528180905</v>
+      </c>
+      <c r="E634" s="0">
+        <v>5</v>
+      </c>
+      <c r="F634" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="B635" s="0">
+        <v>2.2767525211377135</v>
+      </c>
+      <c r="C635" s="0">
+        <v>-2.1742107106900526</v>
+      </c>
+      <c r="D635" s="0">
+        <v>-3.436886431727419</v>
+      </c>
+      <c r="E635" s="0">
+        <v>5</v>
+      </c>
+      <c r="F635" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="B636" s="0">
+        <v>2.4600697784880041</v>
+      </c>
+      <c r="C636" s="0">
+        <v>-0.86826269193034156</v>
+      </c>
+      <c r="D636" s="0">
+        <v>-10.272488194438804</v>
+      </c>
+      <c r="E636" s="0">
+        <v>5</v>
+      </c>
+      <c r="F636" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="B637" s="0">
+        <v>2.6537273183728418</v>
+      </c>
+      <c r="C637" s="0">
+        <v>0.45985610780180691</v>
+      </c>
+      <c r="D637" s="0">
+        <v>-5.7954301847216954</v>
+      </c>
+      <c r="E637" s="0">
+        <v>5</v>
+      </c>
+      <c r="F637" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="B638" s="0">
+        <v>-95.232867486920156</v>
+      </c>
+      <c r="C638" s="0">
+        <v>-97.530633379485607</v>
+      </c>
+      <c r="D638" s="0">
+        <v>0.37324202369688714</v>
+      </c>
+      <c r="E638" s="0">
+        <v>5</v>
+      </c>
+      <c r="F638" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="B639" s="0">
+        <v>3.5463281964558284</v>
+      </c>
+      <c r="C639" s="0">
+        <v>1.38475979021323</v>
+      </c>
+      <c r="D639" s="0">
+        <v>-8.2261320107493905</v>
+      </c>
+      <c r="E639" s="0">
+        <v>5</v>
+      </c>
+      <c r="F639" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="B640" s="0">
+        <v>0.97357671628633036</v>
+      </c>
+      <c r="C640" s="0">
+        <v>-3.4155608372727748</v>
+      </c>
+      <c r="D640" s="0">
+        <v>-4.6728675604247201</v>
+      </c>
+      <c r="E640" s="0">
+        <v>5</v>
+      </c>
+      <c r="F640" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="0" t="s">
+        <v>379</v>
+      </c>
+      <c r="B641" s="0">
+        <v>1.6956443521668156</v>
+      </c>
+      <c r="C641" s="0">
+        <v>0.38254579212903489</v>
+      </c>
+      <c r="D641" s="0">
+        <v>-11.526394868237853</v>
+      </c>
+      <c r="E641" s="0">
+        <v>5</v>
+      </c>
+      <c r="F641" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="0" t="s">
+        <v>343</v>
+      </c>
+      <c r="B642" s="0">
+        <v>0.55060264619280919</v>
+      </c>
+      <c r="C642" s="0">
+        <v>-0.19693153744495287</v>
+      </c>
+      <c r="D642" s="0">
+        <v>-4.7421342297526543</v>
+      </c>
+      <c r="E642" s="0">
+        <v>5</v>
+      </c>
+      <c r="F642" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="B643" s="0">
+        <v>3.210513832651952</v>
+      </c>
+      <c r="C643" s="0">
+        <v>0.7120524406932337</v>
+      </c>
+      <c r="D643" s="0">
+        <v>-8.0232328748475048</v>
+      </c>
+      <c r="E643" s="0">
+        <v>5</v>
+      </c>
+      <c r="F643" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="0" t="s">
+        <v>380</v>
+      </c>
+      <c r="B644" s="0">
+        <v>1.7965264064994844</v>
+      </c>
+      <c r="C644" s="0">
+        <v>0.71571747613694914</v>
+      </c>
+      <c r="D644" s="0">
+        <v>-9.9330138955338931</v>
+      </c>
+      <c r="E644" s="0">
+        <v>5</v>
+      </c>
+      <c r="F644" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="0" t="s">
+        <v>381</v>
+      </c>
+      <c r="B645" s="0">
+        <v>0.38948567622954389</v>
+      </c>
+      <c r="C645" s="0">
+        <v>-0.1302976494026451</v>
+      </c>
+      <c r="D645" s="0">
+        <v>-15.017372001226324</v>
+      </c>
+      <c r="E645" s="0">
+        <v>5</v>
+      </c>
+      <c r="F645" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="0" t="s">
+        <v>382</v>
+      </c>
+      <c r="B646" s="0">
+        <v>-90.80419898440384</v>
+      </c>
+      <c r="C646" s="0">
+        <v>-91.297858167360957</v>
+      </c>
+      <c r="D646" s="0">
+        <v>1.0345992912833535</v>
+      </c>
+      <c r="E646" s="0">
+        <v>5</v>
+      </c>
+      <c r="F646" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="B647" s="0">
+        <v>1.4272992644659372</v>
+      </c>
+      <c r="C647" s="0">
+        <v>-0.55291403751021695</v>
+      </c>
+      <c r="D647" s="0">
+        <v>-1.2861236116453267</v>
+      </c>
+      <c r="E647" s="0">
+        <v>5</v>
+      </c>
+      <c r="F647" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="B648" s="0">
+        <v>2.7789374326117393</v>
+      </c>
+      <c r="C648" s="0">
+        <v>-1.515895233574643</v>
+      </c>
+      <c r="D648" s="0">
+        <v>-1.921083735422654</v>
+      </c>
+      <c r="E648" s="0">
+        <v>5</v>
+      </c>
+      <c r="F648" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="B649" s="0">
+        <v>-2.3635239007921611</v>
+      </c>
+      <c r="C649" s="0">
+        <v>-2.5430571972501839</v>
+      </c>
+      <c r="D649" s="0">
+        <v>-1.4037336250170416</v>
+      </c>
+      <c r="E649" s="0">
+        <v>5</v>
+      </c>
+      <c r="F649" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="0" t="s">
+        <v>383</v>
+      </c>
+      <c r="B650" s="0">
+        <v>-2.4881782886162056</v>
+      </c>
+      <c r="C650" s="0">
+        <v>-0.76505570756269259</v>
+      </c>
+      <c r="D650" s="0">
+        <v>-35.017947914205749</v>
+      </c>
+      <c r="E650" s="0">
+        <v>5</v>
+      </c>
+      <c r="F650" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="0" t="s">
+        <v>231</v>
+      </c>
+      <c r="B651" s="0">
+        <v>1.9821280953704017</v>
+      </c>
+      <c r="C651" s="0">
+        <v>-0.25499188935129996</v>
+      </c>
+      <c r="D651" s="0">
+        <v>-4.8700400710326779</v>
+      </c>
+      <c r="E651" s="0">
+        <v>5</v>
+      </c>
+      <c r="F651" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="0" t="s">
+        <v>384</v>
+      </c>
+      <c r="B652" s="0">
+        <v>1.9752214256948901</v>
+      </c>
+      <c r="C652" s="0">
+        <v>0.060854890003113227</v>
+      </c>
+      <c r="D652" s="0">
+        <v>-4.7724709601202395</v>
+      </c>
+      <c r="E652" s="0">
+        <v>5</v>
+      </c>
+      <c r="F652" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="0" t="s">
+        <v>385</v>
+      </c>
+      <c r="B653" s="0">
+        <v>0.67980844494257853</v>
+      </c>
+      <c r="C653" s="0">
+        <v>0.33552987941522328</v>
+      </c>
+      <c r="D653" s="0">
+        <v>-18.865884941521017</v>
+      </c>
+      <c r="E653" s="0">
+        <v>5</v>
+      </c>
+      <c r="F653" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="0" t="s">
+        <v>386</v>
+      </c>
+      <c r="B654" s="0">
+        <v>-49.753378836707626</v>
+      </c>
+      <c r="C654" s="0">
+        <v>-58.435713006746283</v>
+      </c>
+      <c r="D654" s="0">
+        <v>-2.9668788248365838</v>
+      </c>
+      <c r="E654" s="0">
+        <v>5</v>
+      </c>
+      <c r="F654" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="0" t="s">
+        <v>387</v>
+      </c>
+      <c r="B655" s="0">
+        <v>0.94697138962179472</v>
+      </c>
+      <c r="C655" s="0">
+        <v>-0.12006885102093497</v>
+      </c>
+      <c r="D655" s="0">
+        <v>-2.8204949285481917</v>
+      </c>
+      <c r="E655" s="0">
+        <v>5</v>
+      </c>
+      <c r="F655" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="0" t="s">
+        <v>318</v>
+      </c>
+      <c r="B656" s="0">
+        <v>3.1662039649143612</v>
+      </c>
+      <c r="C656" s="0">
+        <v>0.85325921729147669</v>
+      </c>
+      <c r="D656" s="0">
+        <v>-3.3415427654721253</v>
+      </c>
+      <c r="E656" s="0">
+        <v>5</v>
+      </c>
+      <c r="F656" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B657" s="0">
+        <v>7.673608109770317</v>
+      </c>
+      <c r="C657" s="0">
+        <v>1.1163178197662962</v>
+      </c>
+      <c r="D657" s="0">
+        <v>-41.81537359810806</v>
+      </c>
+      <c r="E657" s="0">
+        <v>5</v>
+      </c>
+      <c r="F657" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="0" t="s">
+        <v>388</v>
+      </c>
+      <c r="B658" s="0">
+        <v>3.1268860044723792</v>
+      </c>
+      <c r="C658" s="0">
+        <v>-0.472882091234961</v>
+      </c>
+      <c r="D658" s="0">
+        <v>-14.986728196250143</v>
+      </c>
+      <c r="E658" s="0">
+        <v>5</v>
+      </c>
+      <c r="F658" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="B659" s="0">
+        <v>2.1060135940814475</v>
+      </c>
+      <c r="C659" s="0">
+        <v>0.17813357075290229</v>
+      </c>
+      <c r="D659" s="0">
+        <v>-6.0350512104253236</v>
+      </c>
+      <c r="E659" s="0">
+        <v>5</v>
+      </c>
+      <c r="F659" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="B660" s="0">
+        <v>4.6762868285396104</v>
+      </c>
+      <c r="C660" s="0">
+        <v>-0.87471093446137094</v>
+      </c>
+      <c r="D660" s="0">
+        <v>-3.7489321612547326</v>
+      </c>
+      <c r="E660" s="0">
+        <v>5</v>
+      </c>
+      <c r="F660" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="0" t="s">
+        <v>389</v>
+      </c>
+      <c r="B661" s="0">
+        <v>-1.1067608078479261</v>
+      </c>
+      <c r="C661" s="0">
+        <v>-3.416982722622119</v>
+      </c>
+      <c r="D661" s="0">
+        <v>-9.8059620421855289</v>
+      </c>
+      <c r="E661" s="0">
+        <v>5</v>
+      </c>
+      <c r="F661" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="0" t="s">
+        <v>390</v>
+      </c>
+      <c r="B662" s="0">
+        <v>3.7265027717608059</v>
+      </c>
+      <c r="C662" s="0">
+        <v>0.88739395315723912</v>
+      </c>
+      <c r="D662" s="0">
+        <v>-4.9420121889019146</v>
+      </c>
+      <c r="E662" s="0">
+        <v>5</v>
+      </c>
+      <c r="F662" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="B663" s="0">
+        <v>2.0567333847238491</v>
+      </c>
+      <c r="C663" s="0">
+        <v>0.53957738399780109</v>
+      </c>
+      <c r="D663" s="0">
+        <v>-8.8866304705067112</v>
+      </c>
+      <c r="E663" s="0">
+        <v>5</v>
+      </c>
+      <c r="F663" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="0" t="s">
+        <v>196</v>
+      </c>
+      <c r="B664" s="0">
+        <v>2.0606852096370738</v>
+      </c>
+      <c r="C664" s="0">
+        <v>-0.84400525520792025</v>
+      </c>
+      <c r="D664" s="0">
+        <v>-4.6233542464916537</v>
+      </c>
+      <c r="E664" s="0">
+        <v>5</v>
+      </c>
+      <c r="F664" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="0" t="s">
+        <v>391</v>
+      </c>
+      <c r="B665" s="0">
+        <v>1.4065864636477516</v>
+      </c>
+      <c r="C665" s="0">
+        <v>-0.30434791838432934</v>
+      </c>
+      <c r="D665" s="0">
+        <v>-3.0444588421880088</v>
+      </c>
+      <c r="E665" s="0">
+        <v>5</v>
+      </c>
+      <c r="F665" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="0" t="s">
+        <v>392</v>
+      </c>
+      <c r="B666" s="0">
+        <v>1.9616515837962871</v>
+      </c>
+      <c r="C666" s="0">
+        <v>0.48223647533883263</v>
+      </c>
+      <c r="D666" s="0">
+        <v>-6.5966634801224444</v>
+      </c>
+      <c r="E666" s="0">
+        <v>5</v>
+      </c>
+      <c r="F666" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="0" t="s">
+        <v>328</v>
+      </c>
+      <c r="B667" s="0">
+        <v>1.2578816321627269</v>
+      </c>
+      <c r="C667" s="0">
+        <v>-1.5946533918404919</v>
+      </c>
+      <c r="D667" s="0">
+        <v>-4.5607731731641037</v>
+      </c>
+      <c r="E667" s="0">
+        <v>5</v>
+      </c>
+      <c r="F667" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="0" t="s">
+        <v>393</v>
+      </c>
+      <c r="B668" s="0">
+        <v>2.1256761271349101</v>
+      </c>
+      <c r="C668" s="0">
+        <v>0.9412856928991109</v>
+      </c>
+      <c r="D668" s="0">
+        <v>-3.0757154925190444</v>
+      </c>
+      <c r="E668" s="0">
+        <v>5</v>
+      </c>
+      <c r="F668" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="0" t="s">
+        <v>325</v>
+      </c>
+      <c r="B669" s="0">
+        <v>6.3460275863970956</v>
+      </c>
+      <c r="C669" s="0">
+        <v>1.7458531000687896</v>
+      </c>
+      <c r="D669" s="0">
+        <v>-8.2328373197529796</v>
+      </c>
+      <c r="E669" s="0">
+        <v>5</v>
+      </c>
+      <c r="F669" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="0" t="s">
+        <v>394</v>
+      </c>
+      <c r="B670" s="0">
+        <v>2.0796044569627932</v>
+      </c>
+      <c r="C670" s="0">
+        <v>0.5993658182819771</v>
+      </c>
+      <c r="D670" s="0">
+        <v>-6.883797803889868</v>
+      </c>
+      <c r="E670" s="0">
+        <v>5</v>
+      </c>
+      <c r="F670" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="0" t="s">
+        <v>395</v>
+      </c>
+      <c r="B671" s="0">
+        <v>-2.8497344199067407</v>
+      </c>
+      <c r="C671" s="0">
+        <v>-4.5083983567620152</v>
+      </c>
+      <c r="D671" s="0">
+        <v>0.75675342045811744</v>
+      </c>
+      <c r="E671" s="0">
+        <v>5</v>
+      </c>
+      <c r="F671" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="B672" s="0">
+        <v>-53.17213197009039</v>
+      </c>
+      <c r="C672" s="0">
+        <v>-61.796230668520643</v>
+      </c>
+      <c r="D672" s="0">
+        <v>-3.7148967322400295</v>
+      </c>
+      <c r="E672" s="0">
+        <v>5</v>
+      </c>
+      <c r="F672" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="B673" s="0">
+        <v>2.0593614410357239</v>
+      </c>
+      <c r="C673" s="0">
+        <v>0.42825026290179036</v>
+      </c>
+      <c r="D673" s="0">
+        <v>-8.574287278940492</v>
+      </c>
+      <c r="E673" s="0">
+        <v>5</v>
+      </c>
+      <c r="F673" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="0" t="s">
+        <v>196</v>
+      </c>
+      <c r="B674" s="0">
+        <v>2.0597554645109462</v>
+      </c>
+      <c r="C674" s="0">
+        <v>0.29032220246176632</v>
+      </c>
+      <c r="D674" s="0">
+        <v>-5.1521342154825431</v>
+      </c>
+      <c r="E674" s="0">
+        <v>5</v>
+      </c>
+      <c r="F674" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="0" t="s">
+        <v>396</v>
+      </c>
+      <c r="B675" s="0">
+        <v>5.9303553185366482</v>
+      </c>
+      <c r="C675" s="0">
+        <v>-0.67626971128058622</v>
+      </c>
+      <c r="D675" s="0">
+        <v>-4.5340704170990414</v>
+      </c>
+      <c r="E675" s="0">
+        <v>5</v>
+      </c>
+      <c r="F675" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B676" s="0">
+        <v>2.6811440492389575</v>
+      </c>
+      <c r="C676" s="0">
+        <v>0.15939277598064949</v>
+      </c>
+      <c r="D676" s="0">
+        <v>-10.913121479125959</v>
+      </c>
+      <c r="E676" s="0">
+        <v>5</v>
+      </c>
+      <c r="F676" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="0" t="s">
+        <v>387</v>
+      </c>
+      <c r="B677" s="0">
+        <v>0.94697138962179472</v>
+      </c>
+      <c r="C677" s="0">
+        <v>-0.12006885102093497</v>
+      </c>
+      <c r="D677" s="0">
+        <v>-2.8204949285481917</v>
+      </c>
+      <c r="E677" s="0">
+        <v>5</v>
+      </c>
+      <c r="F677" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="0" t="s">
+        <v>375</v>
+      </c>
+      <c r="B678" s="0">
+        <v>4.60413049636667</v>
+      </c>
+      <c r="C678" s="0">
+        <v>1.7752387203255642</v>
+      </c>
+      <c r="D678" s="0">
+        <v>-9.3998966474994035</v>
+      </c>
+      <c r="E678" s="0">
+        <v>5</v>
+      </c>
+      <c r="F678" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B679" s="0">
+        <v>10.612651407689375</v>
+      </c>
+      <c r="C679" s="0">
+        <v>2.6064878272623413</v>
+      </c>
+      <c r="D679" s="0">
+        <v>-41.921871312106298</v>
+      </c>
+      <c r="E679" s="0">
+        <v>5</v>
+      </c>
+      <c r="F679" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="0" t="s">
+        <v>388</v>
+      </c>
+      <c r="B680" s="0">
+        <v>3.1268860044723792</v>
+      </c>
+      <c r="C680" s="0">
+        <v>-0.472882091234961</v>
+      </c>
+      <c r="D680" s="0">
+        <v>-14.986728196250143</v>
+      </c>
+      <c r="E680" s="0">
+        <v>5</v>
+      </c>
+      <c r="F680" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="0" t="s">
+        <v>397</v>
+      </c>
+      <c r="B681" s="0">
+        <v>-46.535534055634123</v>
+      </c>
+      <c r="C681" s="0">
+        <v>-40.295026889546541</v>
+      </c>
+      <c r="D681" s="0">
+        <v>3.0059792154236282</v>
+      </c>
+      <c r="E681" s="0">
+        <v>5</v>
+      </c>
+      <c r="F681" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="0" t="s">
+        <v>155</v>
+      </c>
+      <c r="B682" s="0">
+        <v>-0.40418305170142999</v>
+      </c>
+      <c r="C682" s="0">
+        <v>-6.7083424489929406</v>
+      </c>
+      <c r="D682" s="0">
+        <v>0.4967430742035851</v>
+      </c>
+      <c r="E682" s="0">
+        <v>5</v>
+      </c>
+      <c r="F682" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B683" s="0">
+        <v>0.30631924021774332</v>
+      </c>
+      <c r="C683" s="0">
+        <v>1.0298522638412992</v>
+      </c>
+      <c r="D683" s="0">
+        <v>-41.776218552903202</v>
+      </c>
+      <c r="E683" s="0">
+        <v>5</v>
+      </c>
+      <c r="F683" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="0" t="s">
+        <v>397</v>
+      </c>
+      <c r="B684" s="0">
+        <v>-46.535534055634123</v>
+      </c>
+      <c r="C684" s="0">
+        <v>-40.295026889546541</v>
+      </c>
+      <c r="D684" s="0">
+        <v>3.0059792154236282</v>
+      </c>
+      <c r="E684" s="0">
+        <v>5</v>
+      </c>
+      <c r="F684" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="0" t="s">
+        <v>398</v>
+      </c>
+      <c r="B685" s="0">
+        <v>3.9197191472700221</v>
+      </c>
+      <c r="C685" s="0">
+        <v>1.8752795400413631</v>
+      </c>
+      <c r="D685" s="0">
+        <v>-8.3145264052490653</v>
+      </c>
+      <c r="E685" s="0">
+        <v>5</v>
+      </c>
+      <c r="F685" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="0" t="s">
+        <v>399</v>
+      </c>
+      <c r="B686" s="0">
+        <v>3.6628008050642111</v>
+      </c>
+      <c r="C686" s="0">
+        <v>1.0544570750601923</v>
+      </c>
+      <c r="D686" s="0">
+        <v>-7.7354889198463654</v>
+      </c>
+      <c r="E686" s="0">
+        <v>5</v>
+      </c>
+      <c r="F686" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="0" t="s">
+        <v>400</v>
+      </c>
+      <c r="B687" s="0">
+        <v>1.9930564064482876</v>
+      </c>
+      <c r="C687" s="0">
+        <v>1.6073354162282856</v>
+      </c>
+      <c r="D687" s="0">
+        <v>-7.8894642833563555</v>
+      </c>
+      <c r="E687" s="0">
+        <v>5</v>
+      </c>
+      <c r="F687" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="0" t="s">
+        <v>401</v>
+      </c>
+      <c r="B688" s="0">
+        <v>3.9140126939057982</v>
+      </c>
+      <c r="C688" s="0">
+        <v>-1.1342650847522568</v>
+      </c>
+      <c r="D688" s="0">
+        <v>-3.4736175891442564</v>
+      </c>
+      <c r="E688" s="0">
+        <v>5</v>
+      </c>
+      <c r="F688" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="0" t="s">
+        <v>402</v>
+      </c>
+      <c r="B689" s="0">
+        <v>0.19608304662179774</v>
+      </c>
+      <c r="C689" s="0">
+        <v>0.12635324130844178</v>
+      </c>
+      <c r="D689" s="0">
+        <v>-8.3442844911623979</v>
+      </c>
+      <c r="E689" s="0">
+        <v>5</v>
+      </c>
+      <c r="F689" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="0" t="s">
+        <v>403</v>
+      </c>
+      <c r="B690" s="0">
+        <v>3.6740365754280231</v>
+      </c>
+      <c r="C690" s="0">
+        <v>1.6239560143494018</v>
+      </c>
+      <c r="D690" s="0">
+        <v>-7.3852629390437627</v>
+      </c>
+      <c r="E690" s="0">
+        <v>5</v>
+      </c>
+      <c r="F690" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="B691" s="0">
+        <v>2.145085127480749</v>
+      </c>
+      <c r="C691" s="0">
+        <v>-0.80649839008047119</v>
+      </c>
+      <c r="D691" s="0">
+        <v>-2.5192229130575874</v>
+      </c>
+      <c r="E691" s="0">
+        <v>5</v>
+      </c>
+      <c r="F691" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="B692" s="0">
+        <v>2.3113116543087728</v>
+      </c>
+      <c r="C692" s="0">
+        <v>-1.1782054663664245</v>
+      </c>
+      <c r="D692" s="0">
+        <v>-5.83321608558541</v>
+      </c>
+      <c r="E692" s="0">
+        <v>5</v>
+      </c>
+      <c r="F692" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="B693" s="0">
+        <v>2.8940740074732187</v>
+      </c>
+      <c r="C693" s="0">
+        <v>-1.975886776020598</v>
+      </c>
+      <c r="D693" s="0">
+        <v>-3.1022718631726458</v>
+      </c>
+      <c r="E693" s="0">
+        <v>5</v>
+      </c>
+      <c r="F693" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="0" t="s">
+        <v>290</v>
+      </c>
+      <c r="B694" s="0">
+        <v>2.6205282842858009</v>
+      </c>
+      <c r="C694" s="0">
+        <v>0.23775380111287836</v>
+      </c>
+      <c r="D694" s="0">
+        <v>-3.6476884419313422</v>
+      </c>
+      <c r="E694" s="0">
+        <v>5</v>
+      </c>
+      <c r="F694" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="0" t="s">
+        <v>404</v>
+      </c>
+      <c r="B695" s="0">
+        <v>3.2991149450139732</v>
+      </c>
+      <c r="C695" s="0">
+        <v>-0.34562906734083643</v>
+      </c>
+      <c r="D695" s="0">
+        <v>-4.3799308104081609</v>
+      </c>
+      <c r="E695" s="0">
+        <v>5</v>
+      </c>
+      <c r="F695" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="0" t="s">
+        <v>307</v>
+      </c>
+      <c r="B696" s="0">
+        <v>0.91599216327407662</v>
+      </c>
+      <c r="C696" s="0">
+        <v>0.062718810849408488</v>
+      </c>
+      <c r="D696" s="0">
+        <v>-1.9657957988306212</v>
+      </c>
+      <c r="E696" s="0">
+        <v>5</v>
+      </c>
+      <c r="F696" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="B697" s="0">
+        <v>2.2858146156250676</v>
+      </c>
+      <c r="C697" s="0">
+        <v>-1.6871199105490449</v>
+      </c>
+      <c r="D697" s="0">
+        <v>-2.1385927109421972</v>
+      </c>
+      <c r="E697" s="0">
+        <v>5</v>
+      </c>
+      <c r="F697" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="0" t="s">
+        <v>312</v>
+      </c>
+      <c r="B698" s="0">
+        <v>9.102228941972978</v>
+      </c>
+      <c r="C698" s="0">
+        <v>2.1538238884818099</v>
+      </c>
+      <c r="D698" s="0">
+        <v>-8.4613426066990449</v>
+      </c>
+      <c r="E698" s="0">
+        <v>5</v>
+      </c>
+      <c r="F698" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="0" t="s">
+        <v>372</v>
+      </c>
+      <c r="B699" s="0">
+        <v>3.3956524448584098</v>
+      </c>
+      <c r="C699" s="0">
+        <v>1.0087376263601289</v>
+      </c>
+      <c r="D699" s="0">
+        <v>-5.0221610423296941</v>
+      </c>
+      <c r="E699" s="0">
+        <v>5</v>
+      </c>
+      <c r="F699" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="0" t="s">
+        <v>313</v>
+      </c>
+      <c r="B700" s="0">
+        <v>3.6972905264654017</v>
+      </c>
+      <c r="C700" s="0">
+        <v>1.3603621958741527</v>
+      </c>
+      <c r="D700" s="0">
+        <v>-4.7324737035293571</v>
+      </c>
+      <c r="E700" s="0">
+        <v>5</v>
+      </c>
+      <c r="F700" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="B701" s="0">
+        <v>9.0434565422480855</v>
+      </c>
+      <c r="C701" s="0">
+        <v>-1.6557795538868381</v>
+      </c>
+      <c r="D701" s="0">
+        <v>-7.1425591813094185</v>
+      </c>
+      <c r="E701" s="0">
+        <v>5</v>
+      </c>
+      <c r="F701" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="0" t="s">
+        <v>405</v>
+      </c>
+      <c r="B702" s="0">
+        <v>6.3937804833740755</v>
+      </c>
+      <c r="C702" s="0">
+        <v>2.9040640943681804</v>
+      </c>
+      <c r="D702" s="0">
+        <v>-8.1119257609954083</v>
+      </c>
+      <c r="E702" s="0">
+        <v>5</v>
+      </c>
+      <c r="F702" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="0" t="s">
+        <v>406</v>
+      </c>
+      <c r="B703" s="0">
+        <v>0.33457002530473845</v>
+      </c>
+      <c r="C703" s="0">
+        <v>0.022932282052382097</v>
+      </c>
+      <c r="D703" s="0">
+        <v>-1.8962186049399046</v>
+      </c>
+      <c r="E703" s="0">
+        <v>5</v>
+      </c>
+      <c r="F703" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="0" t="s">
+        <v>407</v>
+      </c>
+      <c r="B704" s="0">
+        <v>1.5693755458293426</v>
+      </c>
+      <c r="C704" s="0">
+        <v>-1.1391427527726956</v>
+      </c>
+      <c r="D704" s="0">
+        <v>-4.1056149757191838</v>
+      </c>
+      <c r="E704" s="0">
+        <v>5</v>
+      </c>
+      <c r="F704" s="0" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="B705" s="0">
+        <v>2.3589632416231505</v>
+      </c>
+      <c r="C705" s="0">
+        <v>0.082690366136431132</v>
+      </c>
+      <c r="D705" s="0">
+        <v>-2.3869629621789556</v>
+      </c>
+      <c r="E705" s="0">
+        <v>5</v>
+      </c>
+      <c r="F705" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="B706" s="0">
+        <v>3.0422764778896836</v>
+      </c>
+      <c r="C706" s="0">
+        <v>-0.0030955949094254604</v>
+      </c>
+      <c r="D706" s="0">
+        <v>-3.1176855571215714</v>
+      </c>
+      <c r="E706" s="0">
+        <v>5</v>
+      </c>
+      <c r="F706" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="B707" s="0">
+        <v>2.0001282646859631</v>
+      </c>
+      <c r="C707" s="0">
+        <v>0.53057792575889529</v>
+      </c>
+      <c r="D707" s="0">
+        <v>-3.7393755511579148</v>
+      </c>
+      <c r="E707" s="0">
+        <v>5</v>
+      </c>
+      <c r="F707" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="0" t="s">
+        <v>408</v>
+      </c>
+      <c r="B708" s="0">
+        <v>0.82002409098727147</v>
+      </c>
+      <c r="C708" s="0">
+        <v>-1.4108036465808862</v>
+      </c>
+      <c r="D708" s="0">
+        <v>-1.9236432823270802</v>
+      </c>
+      <c r="E708" s="0">
+        <v>5</v>
+      </c>
+      <c r="F708" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="0" t="s">
+        <v>408</v>
+      </c>
+      <c r="B709" s="0">
+        <v>0.82002409098727147</v>
+      </c>
+      <c r="C709" s="0">
+        <v>-1.4108036465808862</v>
+      </c>
+      <c r="D709" s="0">
+        <v>-1.9236432823270802</v>
+      </c>
+      <c r="E709" s="0">
+        <v>5</v>
+      </c>
+      <c r="F709" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="B710" s="0">
+        <v>1.1977769744269824</v>
+      </c>
+      <c r="C710" s="0">
+        <v>-0.89723042676515696</v>
+      </c>
+      <c r="D710" s="0">
+        <v>-2.3645104756299942</v>
+      </c>
+      <c r="E710" s="0">
+        <v>5</v>
+      </c>
+      <c r="F710" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="0" t="s">
+        <v>409</v>
+      </c>
+      <c r="B711" s="0">
+        <v>0.19296188460702035</v>
+      </c>
+      <c r="C711" s="0">
+        <v>-0.16518747416834315</v>
+      </c>
+      <c r="D711" s="0">
+        <v>-6.3769411941201684</v>
+      </c>
+      <c r="E711" s="0">
+        <v>5</v>
+      </c>
+      <c r="F711" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="B712" s="0">
+        <v>1.910576656428479</v>
+      </c>
+      <c r="C712" s="0">
+        <v>-2.2231653491770573</v>
+      </c>
+      <c r="D712" s="0">
+        <v>-5.5552186124539293</v>
+      </c>
+      <c r="E712" s="0">
+        <v>5</v>
+      </c>
+      <c r="F712" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="0" t="s">
+        <v>410</v>
+      </c>
+      <c r="B713" s="0">
+        <v>1.0364190686713559</v>
+      </c>
+      <c r="C713" s="0">
+        <v>0.76355836917019992</v>
+      </c>
+      <c r="D713" s="0">
+        <v>-7.3334158711781061</v>
+      </c>
+      <c r="E713" s="0">
+        <v>5</v>
+      </c>
+      <c r="F713" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="0" t="s">
+        <v>411</v>
+      </c>
+      <c r="B714" s="0">
+        <v>0.63121067096950578</v>
+      </c>
+      <c r="C714" s="0">
+        <v>-1.4642277995403439</v>
+      </c>
+      <c r="D714" s="0">
+        <v>-1.6573626975350964</v>
+      </c>
+      <c r="E714" s="0">
+        <v>5</v>
+      </c>
+      <c r="F714" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="B715" s="0">
+        <v>1.8175220963631409</v>
+      </c>
+      <c r="C715" s="0">
+        <v>0.069030490485944312</v>
+      </c>
+      <c r="D715" s="0">
+        <v>-4.336864909338777</v>
+      </c>
+      <c r="E715" s="0">
+        <v>5</v>
+      </c>
+      <c r="F715" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="B716" s="0">
+        <v>-1.1733775205861841</v>
+      </c>
+      <c r="C716" s="0">
+        <v>-2.253249873443167</v>
+      </c>
+      <c r="D716" s="0">
+        <v>-2.0552904369955551</v>
+      </c>
+      <c r="E716" s="0">
+        <v>5</v>
+      </c>
+      <c r="F716" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="B717" s="0">
+        <v>-0.41879479948172593</v>
+      </c>
+      <c r="C717" s="0">
+        <v>-2.1038766353955798</v>
+      </c>
+      <c r="D717" s="0">
+        <v>-2.2695558233134245</v>
+      </c>
+      <c r="E717" s="0">
+        <v>5</v>
+      </c>
+      <c r="F717" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="B718" s="0">
+        <v>2.5357015577626378</v>
+      </c>
+      <c r="C718" s="0">
+        <v>1.3302415528836025</v>
+      </c>
+      <c r="D718" s="0">
+        <v>-4.1663477851383117</v>
+      </c>
+      <c r="E718" s="0">
+        <v>5</v>
+      </c>
+      <c r="F718" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="B719" s="0">
+        <v>1.2833706414360644</v>
+      </c>
+      <c r="C719" s="0">
+        <v>1.3970556084800951</v>
+      </c>
+      <c r="D719" s="0">
+        <v>-2.1204594627309494</v>
+      </c>
+      <c r="E719" s="0">
+        <v>5</v>
+      </c>
+      <c r="F719" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="B720" s="0">
+        <v>-1.2834524822167142</v>
+      </c>
+      <c r="C720" s="0">
+        <v>-0.045323404254654212</v>
+      </c>
+      <c r="D720" s="0">
+        <v>-0.010854335535106507</v>
+      </c>
+      <c r="E720" s="0">
+        <v>5</v>
+      </c>
+      <c r="F720" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="B721" s="0">
+        <v>0.91567587602952838</v>
+      </c>
+      <c r="C721" s="0">
+        <v>0.27397616244162049</v>
+      </c>
+      <c r="D721" s="0">
+        <v>-6.4965731578690624</v>
+      </c>
+      <c r="E721" s="0">
+        <v>5</v>
+      </c>
+      <c r="F721" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="B722" s="0">
+        <v>1.8175220963631409</v>
+      </c>
+      <c r="C722" s="0">
+        <v>0.069030490485944312</v>
+      </c>
+      <c r="D722" s="0">
+        <v>-4.336864909338777</v>
+      </c>
+      <c r="E722" s="0">
+        <v>5</v>
+      </c>
+      <c r="F722" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>